--- a/dist/_sh_excel_test.xlsx
+++ b/dist/_sh_excel_test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="480">
   <si>
     <t>태양광 발전사업</t>
   </si>
@@ -915,7 +915,7 @@
     <t>E50</t>
   </si>
   <si>
-    <t xml:space="preserve">  지출 비중 · unit</t>
+    <t xml:space="preserve">  지출 비중</t>
   </si>
   <si>
     <t>입력값 57행</t>
@@ -3241,8 +3241,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:90" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="33" t="s">
         <v>188</v>
       </c>
@@ -4844,244 +4843,244 @@
         <f>J105*$D$88*100</f>
       </c>
       <c r="K8" s="31">
-        <f>K105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="L8" s="31">
-        <f>L105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="M8" s="31">
-        <f>M105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="N8" s="31">
-        <f>N105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="O8" s="31">
-        <f>O105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="P8" s="31">
-        <f>P105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="Q8" s="31">
-        <f>Q105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="R8" s="31">
-        <f>R105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="S8" s="31">
-        <f>S105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="T8" s="31">
-        <f>T105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="U8" s="31">
-        <f>U105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="V8" s="31">
-        <f>V105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="W8" s="31">
-        <f>W105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="X8" s="31">
-        <f>X105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="Y8" s="31">
-        <f>Y105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <f>Z105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AA8" s="31">
-        <f>AA105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AB8" s="31">
-        <f>AB105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AC8" s="31">
-        <f>AC105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AD8" s="31">
-        <f>AD105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AE8" s="31">
-        <f>AE105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AF8" s="31">
-        <f>AF105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AG8" s="31">
-        <f>AG105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AH8" s="31">
-        <f>AH105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AI8" s="31">
-        <f>AI105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AJ8" s="31">
-        <f>AJ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AK8" s="31">
-        <f>AK105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AL8" s="31">
-        <f>AL105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AM8" s="31">
-        <f>AM105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AN8" s="31">
-        <f>AN105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AO8" s="31">
-        <f>AO105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AP8" s="31">
-        <f>AP105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AQ8" s="31">
-        <f>AQ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AR8" s="31">
-        <f>AR105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AS8" s="31">
-        <f>AS105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AT8" s="31">
-        <f>AT105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AU8" s="31">
-        <f>AU105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f>AV105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AW8" s="31">
-        <f>AW105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AX8" s="31">
-        <f>AX105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AY8" s="31">
-        <f>AY105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="AZ8" s="31">
-        <f>AZ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BA8" s="31">
-        <f>BA105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BB8" s="31">
-        <f>BB105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BC8" s="31">
-        <f>BC105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BD8" s="31">
-        <f>BD105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BE8" s="31">
-        <f>BE105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BF8" s="31">
-        <f>BF105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BG8" s="31">
-        <f>BG105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BH8" s="31">
-        <f>BH105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BI8" s="31">
-        <f>BI105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BJ8" s="31">
-        <f>BJ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BK8" s="31">
-        <f>BK105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BL8" s="31">
-        <f>BL105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BM8" s="31">
-        <f>BM105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BN8" s="31">
-        <f>BN105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BO8" s="31">
-        <f>BO105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BP8" s="31">
-        <f>BP105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BQ8" s="31">
-        <f>BQ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BR8" s="31">
-        <f>BR105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BS8" s="31">
-        <f>BS105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BT8" s="31">
-        <f>BT105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BU8" s="31">
-        <f>BU105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BV8" s="31">
-        <f>BV105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BW8" s="31">
-        <f>BW105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BX8" s="31">
-        <f>BX105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BY8" s="31">
-        <f>BY105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="BZ8" s="31">
-        <f>BZ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CA8" s="31">
-        <f>CA105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CB8" s="31">
-        <f>CB105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CC8" s="31">
-        <f>CC105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CD8" s="31">
-        <f>CD105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CE8" s="31">
-        <f>CE105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CF8" s="31">
-        <f>CF105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CG8" s="31">
-        <f>CG105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CH8" s="31">
-        <f>CH105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CI8" s="31">
-        <f>CI105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CJ8" s="31">
-        <f>CJ105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CK8" s="31">
-        <f>CK105*$D$88*100</f>
+        <v>0</v>
       </c>
       <c r="CL8" s="31">
-        <f>CL105*$D$88*100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:90" x14ac:dyDescent="0.25">
@@ -20040,7 +20039,7 @@
         <f>'입력값'!E50</f>
       </c>
     </row>
-    <row r="105" spans="2:90" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="33" t="s">
         <v>298</v>
       </c>
@@ -20064,246 +20063,6 @@
       </c>
       <c r="J105" s="53">
         <f>'입력값'!J57</f>
-      </c>
-      <c r="K105" s="45">
-        <f>'입력값'!K57</f>
-      </c>
-      <c r="L105" s="45">
-        <f>'입력값'!L57</f>
-      </c>
-      <c r="M105" s="45">
-        <f>'입력값'!M57</f>
-      </c>
-      <c r="N105" s="45">
-        <f>'입력값'!N57</f>
-      </c>
-      <c r="O105" s="45">
-        <f>'입력값'!O57</f>
-      </c>
-      <c r="P105" s="45">
-        <f>'입력값'!P57</f>
-      </c>
-      <c r="Q105" s="45">
-        <f>'입력값'!Q57</f>
-      </c>
-      <c r="R105" s="45">
-        <f>'입력값'!R57</f>
-      </c>
-      <c r="S105" s="45">
-        <f>'입력값'!S57</f>
-      </c>
-      <c r="T105" s="45">
-        <f>'입력값'!T57</f>
-      </c>
-      <c r="U105" s="45">
-        <f>'입력값'!U57</f>
-      </c>
-      <c r="V105" s="45">
-        <f>'입력값'!V57</f>
-      </c>
-      <c r="W105" s="45">
-        <f>'입력값'!W57</f>
-      </c>
-      <c r="X105" s="45">
-        <f>'입력값'!X57</f>
-      </c>
-      <c r="Y105" s="45">
-        <f>'입력값'!Y57</f>
-      </c>
-      <c r="Z105" s="45">
-        <f>'입력값'!Z57</f>
-      </c>
-      <c r="AA105" s="45">
-        <f>'입력값'!AA57</f>
-      </c>
-      <c r="AB105" s="45">
-        <f>'입력값'!AB57</f>
-      </c>
-      <c r="AC105" s="45">
-        <f>'입력값'!AC57</f>
-      </c>
-      <c r="AD105" s="45">
-        <f>'입력값'!AD57</f>
-      </c>
-      <c r="AE105" s="45">
-        <f>'입력값'!AE57</f>
-      </c>
-      <c r="AF105" s="45">
-        <f>'입력값'!AF57</f>
-      </c>
-      <c r="AG105" s="45">
-        <f>'입력값'!AG57</f>
-      </c>
-      <c r="AH105" s="45">
-        <f>'입력값'!AH57</f>
-      </c>
-      <c r="AI105" s="45">
-        <f>'입력값'!AI57</f>
-      </c>
-      <c r="AJ105" s="45">
-        <f>'입력값'!AJ57</f>
-      </c>
-      <c r="AK105" s="45">
-        <f>'입력값'!AK57</f>
-      </c>
-      <c r="AL105" s="45">
-        <f>'입력값'!AL57</f>
-      </c>
-      <c r="AM105" s="45">
-        <f>'입력값'!AM57</f>
-      </c>
-      <c r="AN105" s="45">
-        <f>'입력값'!AN57</f>
-      </c>
-      <c r="AO105" s="45">
-        <f>'입력값'!AO57</f>
-      </c>
-      <c r="AP105" s="45">
-        <f>'입력값'!AP57</f>
-      </c>
-      <c r="AQ105" s="45">
-        <f>'입력값'!AQ57</f>
-      </c>
-      <c r="AR105" s="45">
-        <f>'입력값'!AR57</f>
-      </c>
-      <c r="AS105" s="45">
-        <f>'입력값'!AS57</f>
-      </c>
-      <c r="AT105" s="45">
-        <f>'입력값'!AT57</f>
-      </c>
-      <c r="AU105" s="45">
-        <f>'입력값'!AU57</f>
-      </c>
-      <c r="AV105" s="45">
-        <f>'입력값'!AV57</f>
-      </c>
-      <c r="AW105" s="45">
-        <f>'입력값'!AW57</f>
-      </c>
-      <c r="AX105" s="45">
-        <f>'입력값'!AX57</f>
-      </c>
-      <c r="AY105" s="45">
-        <f>'입력값'!AY57</f>
-      </c>
-      <c r="AZ105" s="45">
-        <f>'입력값'!AZ57</f>
-      </c>
-      <c r="BA105" s="45">
-        <f>'입력값'!BA57</f>
-      </c>
-      <c r="BB105" s="45">
-        <f>'입력값'!BB57</f>
-      </c>
-      <c r="BC105" s="45">
-        <f>'입력값'!BC57</f>
-      </c>
-      <c r="BD105" s="45">
-        <f>'입력값'!BD57</f>
-      </c>
-      <c r="BE105" s="45">
-        <f>'입력값'!BE57</f>
-      </c>
-      <c r="BF105" s="45">
-        <f>'입력값'!BF57</f>
-      </c>
-      <c r="BG105" s="45">
-        <f>'입력값'!BG57</f>
-      </c>
-      <c r="BH105" s="45">
-        <f>'입력값'!BH57</f>
-      </c>
-      <c r="BI105" s="45">
-        <f>'입력값'!BI57</f>
-      </c>
-      <c r="BJ105" s="45">
-        <f>'입력값'!BJ57</f>
-      </c>
-      <c r="BK105" s="45">
-        <f>'입력값'!BK57</f>
-      </c>
-      <c r="BL105" s="45">
-        <f>'입력값'!BL57</f>
-      </c>
-      <c r="BM105" s="45">
-        <f>'입력값'!BM57</f>
-      </c>
-      <c r="BN105" s="45">
-        <f>'입력값'!BN57</f>
-      </c>
-      <c r="BO105" s="45">
-        <f>'입력값'!BO57</f>
-      </c>
-      <c r="BP105" s="45">
-        <f>'입력값'!BP57</f>
-      </c>
-      <c r="BQ105" s="45">
-        <f>'입력값'!BQ57</f>
-      </c>
-      <c r="BR105" s="45">
-        <f>'입력값'!BR57</f>
-      </c>
-      <c r="BS105" s="45">
-        <f>'입력값'!BS57</f>
-      </c>
-      <c r="BT105" s="45">
-        <f>'입력값'!BT57</f>
-      </c>
-      <c r="BU105" s="45">
-        <f>'입력값'!BU57</f>
-      </c>
-      <c r="BV105" s="45">
-        <f>'입력값'!BV57</f>
-      </c>
-      <c r="BW105" s="45">
-        <f>'입력값'!BW57</f>
-      </c>
-      <c r="BX105" s="45">
-        <f>'입력값'!BX57</f>
-      </c>
-      <c r="BY105" s="45">
-        <f>'입력값'!BY57</f>
-      </c>
-      <c r="BZ105" s="45">
-        <f>'입력값'!BZ57</f>
-      </c>
-      <c r="CA105" s="45">
-        <f>'입력값'!CA57</f>
-      </c>
-      <c r="CB105" s="45">
-        <f>'입력값'!CB57</f>
-      </c>
-      <c r="CC105" s="45">
-        <f>'입력값'!CC57</f>
-      </c>
-      <c r="CD105" s="45">
-        <f>'입력값'!CD57</f>
-      </c>
-      <c r="CE105" s="45">
-        <f>'입력값'!CE57</f>
-      </c>
-      <c r="CF105" s="45">
-        <f>'입력값'!CF57</f>
-      </c>
-      <c r="CG105" s="45">
-        <f>'입력값'!CG57</f>
-      </c>
-      <c r="CH105" s="45">
-        <f>'입력값'!CH57</f>
-      </c>
-      <c r="CI105" s="45">
-        <f>'입력값'!CI57</f>
-      </c>
-      <c r="CJ105" s="45">
-        <f>'입력값'!CJ57</f>
-      </c>
-      <c r="CK105" s="45">
-        <f>'입력값'!CK57</f>
-      </c>
-      <c r="CL105" s="45">
-        <f>'입력값'!CL57</f>
       </c>
     </row>
   </sheetData>
@@ -32194,7 +31953,7 @@
   <sheetPr>
     <tabColor rgb="FF2E7D62"/>
   </sheetPr>
-  <dimension ref="A1:CM79"/>
+  <dimension ref="A1:CM77"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -33609,7 +33368,7 @@
         <f>CK9-CK10-CK14-'Opex'!CK23+CK19</f>
       </c>
       <c r="CL13" s="14">
-        <f>CL9-CL10-CL14-'Opex'!CL23-$D$74*100+CL19</f>
+        <f>CL9-CL10-CL14-'Opex'!CL23-$D$73*100+CL19</f>
       </c>
     </row>
     <row r="14" spans="2:90" x14ac:dyDescent="0.25">
@@ -34176,241 +33935,241 @@
         <f>0</f>
       </c>
       <c r="K16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(K11),K11&gt;=$D$76),OR(ISBLANK(K48),K48&gt;=$D$77)),MAX(0,K18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(K11),K11&gt;=$D$75),OR(ISBLANK(K48),K48&gt;=$D$76)),MAX(0,K18-$D$74*100),0)</f>
       </c>
       <c r="L16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(L11),L11&gt;=$D$76),OR(ISBLANK(L48),L48&gt;=$D$77)),MAX(0,L18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(L11),L11&gt;=$D$75),OR(ISBLANK(L48),L48&gt;=$D$76)),MAX(0,L18-$D$74*100),0)</f>
       </c>
       <c r="M16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(M11),M11&gt;=$D$76),OR(ISBLANK(M48),M48&gt;=$D$77)),MAX(0,M18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(M11),M11&gt;=$D$75),OR(ISBLANK(M48),M48&gt;=$D$76)),MAX(0,M18-$D$74*100),0)</f>
       </c>
       <c r="N16" s="42">
-        <f>IF(AND(0&gt;=($D$78-1),OR(ISBLANK(N11),N11&gt;=$D$76),OR(ISBLANK(N48),N48&gt;=$D$77)),MAX(0,N18-$D$75*100),0)</f>
+        <f>IF(AND(0&gt;=($D$77-1),OR(ISBLANK(N11),N11&gt;=$D$75),OR(ISBLANK(N48),N48&gt;=$D$76)),MAX(0,N18-$D$74*100),0)</f>
       </c>
       <c r="O16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(O11),O11&gt;=$D$76),OR(ISBLANK(O48),O48&gt;=$D$77)),MAX(0,O18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(O11),O11&gt;=$D$75),OR(ISBLANK(O48),O48&gt;=$D$76)),MAX(0,O18-$D$74*100),0)</f>
       </c>
       <c r="P16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(P11),P11&gt;=$D$76),OR(ISBLANK(P48),P48&gt;=$D$77)),MAX(0,P18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(P11),P11&gt;=$D$75),OR(ISBLANK(P48),P48&gt;=$D$76)),MAX(0,P18-$D$74*100),0)</f>
       </c>
       <c r="Q16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(Q11),Q11&gt;=$D$76),OR(ISBLANK(Q48),Q48&gt;=$D$77)),MAX(0,Q18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(Q11),Q11&gt;=$D$75),OR(ISBLANK(Q48),Q48&gt;=$D$76)),MAX(0,Q18-$D$74*100),0)</f>
       </c>
       <c r="R16" s="42">
-        <f>IF(AND(1&gt;=($D$78-1),OR(ISBLANK(R11),R11&gt;=$D$76),OR(ISBLANK(R48),R48&gt;=$D$77)),MAX(0,R18-$D$75*100),0)</f>
+        <f>IF(AND(1&gt;=($D$77-1),OR(ISBLANK(R11),R11&gt;=$D$75),OR(ISBLANK(R48),R48&gt;=$D$76)),MAX(0,R18-$D$74*100),0)</f>
       </c>
       <c r="S16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(S11),S11&gt;=$D$76),OR(ISBLANK(S48),S48&gt;=$D$77)),MAX(0,S18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(S11),S11&gt;=$D$75),OR(ISBLANK(S48),S48&gt;=$D$76)),MAX(0,S18-$D$74*100),0)</f>
       </c>
       <c r="T16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(T11),T11&gt;=$D$76),OR(ISBLANK(T48),T48&gt;=$D$77)),MAX(0,T18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(T11),T11&gt;=$D$75),OR(ISBLANK(T48),T48&gt;=$D$76)),MAX(0,T18-$D$74*100),0)</f>
       </c>
       <c r="U16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(U11),U11&gt;=$D$76),OR(ISBLANK(U48),U48&gt;=$D$77)),MAX(0,U18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(U11),U11&gt;=$D$75),OR(ISBLANK(U48),U48&gt;=$D$76)),MAX(0,U18-$D$74*100),0)</f>
       </c>
       <c r="V16" s="42">
-        <f>IF(AND(2&gt;=($D$78-1),OR(ISBLANK(V11),V11&gt;=$D$76),OR(ISBLANK(V48),V48&gt;=$D$77)),MAX(0,V18-$D$75*100),0)</f>
+        <f>IF(AND(2&gt;=($D$77-1),OR(ISBLANK(V11),V11&gt;=$D$75),OR(ISBLANK(V48),V48&gt;=$D$76)),MAX(0,V18-$D$74*100),0)</f>
       </c>
       <c r="W16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(W11),W11&gt;=$D$76),OR(ISBLANK(W48),W48&gt;=$D$77)),MAX(0,W18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(W11),W11&gt;=$D$75),OR(ISBLANK(W48),W48&gt;=$D$76)),MAX(0,W18-$D$74*100),0)</f>
       </c>
       <c r="X16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(X11),X11&gt;=$D$76),OR(ISBLANK(X48),X48&gt;=$D$77)),MAX(0,X18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(X11),X11&gt;=$D$75),OR(ISBLANK(X48),X48&gt;=$D$76)),MAX(0,X18-$D$74*100),0)</f>
       </c>
       <c r="Y16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(Y11),Y11&gt;=$D$76),OR(ISBLANK(Y48),Y48&gt;=$D$77)),MAX(0,Y18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(Y11),Y11&gt;=$D$75),OR(ISBLANK(Y48),Y48&gt;=$D$76)),MAX(0,Y18-$D$74*100),0)</f>
       </c>
       <c r="Z16" s="42">
-        <f>IF(AND(3&gt;=($D$78-1),OR(ISBLANK(Z11),Z11&gt;=$D$76),OR(ISBLANK(Z48),Z48&gt;=$D$77)),MAX(0,Z18-$D$75*100),0)</f>
+        <f>IF(AND(3&gt;=($D$77-1),OR(ISBLANK(Z11),Z11&gt;=$D$75),OR(ISBLANK(Z48),Z48&gt;=$D$76)),MAX(0,Z18-$D$74*100),0)</f>
       </c>
       <c r="AA16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AA11),AA11&gt;=$D$76),OR(ISBLANK(AA48),AA48&gt;=$D$77)),MAX(0,AA18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AA11),AA11&gt;=$D$75),OR(ISBLANK(AA48),AA48&gt;=$D$76)),MAX(0,AA18-$D$74*100),0)</f>
       </c>
       <c r="AB16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AB11),AB11&gt;=$D$76),OR(ISBLANK(AB48),AB48&gt;=$D$77)),MAX(0,AB18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AB11),AB11&gt;=$D$75),OR(ISBLANK(AB48),AB48&gt;=$D$76)),MAX(0,AB18-$D$74*100),0)</f>
       </c>
       <c r="AC16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AC11),AC11&gt;=$D$76),OR(ISBLANK(AC48),AC48&gt;=$D$77)),MAX(0,AC18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AC11),AC11&gt;=$D$75),OR(ISBLANK(AC48),AC48&gt;=$D$76)),MAX(0,AC18-$D$74*100),0)</f>
       </c>
       <c r="AD16" s="42">
-        <f>IF(AND(4&gt;=($D$78-1),OR(ISBLANK(AD11),AD11&gt;=$D$76),OR(ISBLANK(AD48),AD48&gt;=$D$77)),MAX(0,AD18-$D$75*100),0)</f>
+        <f>IF(AND(4&gt;=($D$77-1),OR(ISBLANK(AD11),AD11&gt;=$D$75),OR(ISBLANK(AD48),AD48&gt;=$D$76)),MAX(0,AD18-$D$74*100),0)</f>
       </c>
       <c r="AE16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AE11),AE11&gt;=$D$76),OR(ISBLANK(AE48),AE48&gt;=$D$77)),MAX(0,AE18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AE11),AE11&gt;=$D$75),OR(ISBLANK(AE48),AE48&gt;=$D$76)),MAX(0,AE18-$D$74*100),0)</f>
       </c>
       <c r="AF16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AF11),AF11&gt;=$D$76),OR(ISBLANK(AF48),AF48&gt;=$D$77)),MAX(0,AF18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AF11),AF11&gt;=$D$75),OR(ISBLANK(AF48),AF48&gt;=$D$76)),MAX(0,AF18-$D$74*100),0)</f>
       </c>
       <c r="AG16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AG11),AG11&gt;=$D$76),OR(ISBLANK(AG48),AG48&gt;=$D$77)),MAX(0,AG18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AG11),AG11&gt;=$D$75),OR(ISBLANK(AG48),AG48&gt;=$D$76)),MAX(0,AG18-$D$74*100),0)</f>
       </c>
       <c r="AH16" s="42">
-        <f>IF(AND(5&gt;=($D$78-1),OR(ISBLANK(AH11),AH11&gt;=$D$76),OR(ISBLANK(AH48),AH48&gt;=$D$77)),MAX(0,AH18-$D$75*100),0)</f>
+        <f>IF(AND(5&gt;=($D$77-1),OR(ISBLANK(AH11),AH11&gt;=$D$75),OR(ISBLANK(AH48),AH48&gt;=$D$76)),MAX(0,AH18-$D$74*100),0)</f>
       </c>
       <c r="AI16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AI11),AI11&gt;=$D$76),OR(ISBLANK(AI48),AI48&gt;=$D$77)),MAX(0,AI18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AI11),AI11&gt;=$D$75),OR(ISBLANK(AI48),AI48&gt;=$D$76)),MAX(0,AI18-$D$74*100),0)</f>
       </c>
       <c r="AJ16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AJ11),AJ11&gt;=$D$76),OR(ISBLANK(AJ48),AJ48&gt;=$D$77)),MAX(0,AJ18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AJ11),AJ11&gt;=$D$75),OR(ISBLANK(AJ48),AJ48&gt;=$D$76)),MAX(0,AJ18-$D$74*100),0)</f>
       </c>
       <c r="AK16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AK11),AK11&gt;=$D$76),OR(ISBLANK(AK48),AK48&gt;=$D$77)),MAX(0,AK18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AK11),AK11&gt;=$D$75),OR(ISBLANK(AK48),AK48&gt;=$D$76)),MAX(0,AK18-$D$74*100),0)</f>
       </c>
       <c r="AL16" s="42">
-        <f>IF(AND(6&gt;=($D$78-1),OR(ISBLANK(AL11),AL11&gt;=$D$76),OR(ISBLANK(AL48),AL48&gt;=$D$77)),MAX(0,AL18-$D$75*100),0)</f>
+        <f>IF(AND(6&gt;=($D$77-1),OR(ISBLANK(AL11),AL11&gt;=$D$75),OR(ISBLANK(AL48),AL48&gt;=$D$76)),MAX(0,AL18-$D$74*100),0)</f>
       </c>
       <c r="AM16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AM11),AM11&gt;=$D$76),OR(ISBLANK(AM48),AM48&gt;=$D$77)),MAX(0,AM18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AM11),AM11&gt;=$D$75),OR(ISBLANK(AM48),AM48&gt;=$D$76)),MAX(0,AM18-$D$74*100),0)</f>
       </c>
       <c r="AN16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AN11),AN11&gt;=$D$76),OR(ISBLANK(AN48),AN48&gt;=$D$77)),MAX(0,AN18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AN11),AN11&gt;=$D$75),OR(ISBLANK(AN48),AN48&gt;=$D$76)),MAX(0,AN18-$D$74*100),0)</f>
       </c>
       <c r="AO16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AO11),AO11&gt;=$D$76),OR(ISBLANK(AO48),AO48&gt;=$D$77)),MAX(0,AO18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AO11),AO11&gt;=$D$75),OR(ISBLANK(AO48),AO48&gt;=$D$76)),MAX(0,AO18-$D$74*100),0)</f>
       </c>
       <c r="AP16" s="42">
-        <f>IF(AND(7&gt;=($D$78-1),OR(ISBLANK(AP11),AP11&gt;=$D$76),OR(ISBLANK(AP48),AP48&gt;=$D$77)),MAX(0,AP18-$D$75*100),0)</f>
+        <f>IF(AND(7&gt;=($D$77-1),OR(ISBLANK(AP11),AP11&gt;=$D$75),OR(ISBLANK(AP48),AP48&gt;=$D$76)),MAX(0,AP18-$D$74*100),0)</f>
       </c>
       <c r="AQ16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AQ11),AQ11&gt;=$D$76),OR(ISBLANK(AQ48),AQ48&gt;=$D$77)),MAX(0,AQ18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AQ11),AQ11&gt;=$D$75),OR(ISBLANK(AQ48),AQ48&gt;=$D$76)),MAX(0,AQ18-$D$74*100),0)</f>
       </c>
       <c r="AR16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AR11),AR11&gt;=$D$76),OR(ISBLANK(AR48),AR48&gt;=$D$77)),MAX(0,AR18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AR11),AR11&gt;=$D$75),OR(ISBLANK(AR48),AR48&gt;=$D$76)),MAX(0,AR18-$D$74*100),0)</f>
       </c>
       <c r="AS16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AS11),AS11&gt;=$D$76),OR(ISBLANK(AS48),AS48&gt;=$D$77)),MAX(0,AS18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AS11),AS11&gt;=$D$75),OR(ISBLANK(AS48),AS48&gt;=$D$76)),MAX(0,AS18-$D$74*100),0)</f>
       </c>
       <c r="AT16" s="42">
-        <f>IF(AND(8&gt;=($D$78-1),OR(ISBLANK(AT11),AT11&gt;=$D$76),OR(ISBLANK(AT48),AT48&gt;=$D$77)),MAX(0,AT18-$D$75*100),0)</f>
+        <f>IF(AND(8&gt;=($D$77-1),OR(ISBLANK(AT11),AT11&gt;=$D$75),OR(ISBLANK(AT48),AT48&gt;=$D$76)),MAX(0,AT18-$D$74*100),0)</f>
       </c>
       <c r="AU16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AU11),AU11&gt;=$D$76),OR(ISBLANK(AU48),AU48&gt;=$D$77)),MAX(0,AU18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AU11),AU11&gt;=$D$75),OR(ISBLANK(AU48),AU48&gt;=$D$76)),MAX(0,AU18-$D$74*100),0)</f>
       </c>
       <c r="AV16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AV11),AV11&gt;=$D$76),OR(ISBLANK(AV48),AV48&gt;=$D$77)),MAX(0,AV18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AV11),AV11&gt;=$D$75),OR(ISBLANK(AV48),AV48&gt;=$D$76)),MAX(0,AV18-$D$74*100),0)</f>
       </c>
       <c r="AW16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AW11),AW11&gt;=$D$76),OR(ISBLANK(AW48),AW48&gt;=$D$77)),MAX(0,AW18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AW11),AW11&gt;=$D$75),OR(ISBLANK(AW48),AW48&gt;=$D$76)),MAX(0,AW18-$D$74*100),0)</f>
       </c>
       <c r="AX16" s="42">
-        <f>IF(AND(9&gt;=($D$78-1),OR(ISBLANK(AX11),AX11&gt;=$D$76),OR(ISBLANK(AX48),AX48&gt;=$D$77)),MAX(0,AX18-$D$75*100),0)</f>
+        <f>IF(AND(9&gt;=($D$77-1),OR(ISBLANK(AX11),AX11&gt;=$D$75),OR(ISBLANK(AX48),AX48&gt;=$D$76)),MAX(0,AX18-$D$74*100),0)</f>
       </c>
       <c r="AY16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(AY11),AY11&gt;=$D$76),OR(ISBLANK(AY48),AY48&gt;=$D$77)),MAX(0,AY18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(AY11),AY11&gt;=$D$75),OR(ISBLANK(AY48),AY48&gt;=$D$76)),MAX(0,AY18-$D$74*100),0)</f>
       </c>
       <c r="AZ16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(AZ11),AZ11&gt;=$D$76),OR(ISBLANK(AZ48),AZ48&gt;=$D$77)),MAX(0,AZ18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(AZ11),AZ11&gt;=$D$75),OR(ISBLANK(AZ48),AZ48&gt;=$D$76)),MAX(0,AZ18-$D$74*100),0)</f>
       </c>
       <c r="BA16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(BA11),BA11&gt;=$D$76),OR(ISBLANK(BA48),BA48&gt;=$D$77)),MAX(0,BA18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(BA11),BA11&gt;=$D$75),OR(ISBLANK(BA48),BA48&gt;=$D$76)),MAX(0,BA18-$D$74*100),0)</f>
       </c>
       <c r="BB16" s="42">
-        <f>IF(AND(10&gt;=($D$78-1),OR(ISBLANK(BB11),BB11&gt;=$D$76),OR(ISBLANK(BB48),BB48&gt;=$D$77)),MAX(0,BB18-$D$75*100),0)</f>
+        <f>IF(AND(10&gt;=($D$77-1),OR(ISBLANK(BB11),BB11&gt;=$D$75),OR(ISBLANK(BB48),BB48&gt;=$D$76)),MAX(0,BB18-$D$74*100),0)</f>
       </c>
       <c r="BC16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BC11),BC11&gt;=$D$76),OR(ISBLANK(BC48),BC48&gt;=$D$77)),MAX(0,BC18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BC11),BC11&gt;=$D$75),OR(ISBLANK(BC48),BC48&gt;=$D$76)),MAX(0,BC18-$D$74*100),0)</f>
       </c>
       <c r="BD16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BD11),BD11&gt;=$D$76),OR(ISBLANK(BD48),BD48&gt;=$D$77)),MAX(0,BD18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BD11),BD11&gt;=$D$75),OR(ISBLANK(BD48),BD48&gt;=$D$76)),MAX(0,BD18-$D$74*100),0)</f>
       </c>
       <c r="BE16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BE11),BE11&gt;=$D$76),OR(ISBLANK(BE48),BE48&gt;=$D$77)),MAX(0,BE18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BE11),BE11&gt;=$D$75),OR(ISBLANK(BE48),BE48&gt;=$D$76)),MAX(0,BE18-$D$74*100),0)</f>
       </c>
       <c r="BF16" s="42">
-        <f>IF(AND(11&gt;=($D$78-1),OR(ISBLANK(BF11),BF11&gt;=$D$76),OR(ISBLANK(BF48),BF48&gt;=$D$77)),MAX(0,BF18-$D$75*100),0)</f>
+        <f>IF(AND(11&gt;=($D$77-1),OR(ISBLANK(BF11),BF11&gt;=$D$75),OR(ISBLANK(BF48),BF48&gt;=$D$76)),MAX(0,BF18-$D$74*100),0)</f>
       </c>
       <c r="BG16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BG11),BG11&gt;=$D$76),OR(ISBLANK(BG48),BG48&gt;=$D$77)),MAX(0,BG18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BG11),BG11&gt;=$D$75),OR(ISBLANK(BG48),BG48&gt;=$D$76)),MAX(0,BG18-$D$74*100),0)</f>
       </c>
       <c r="BH16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BH11),BH11&gt;=$D$76),OR(ISBLANK(BH48),BH48&gt;=$D$77)),MAX(0,BH18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BH11),BH11&gt;=$D$75),OR(ISBLANK(BH48),BH48&gt;=$D$76)),MAX(0,BH18-$D$74*100),0)</f>
       </c>
       <c r="BI16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BI11),BI11&gt;=$D$76),OR(ISBLANK(BI48),BI48&gt;=$D$77)),MAX(0,BI18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BI11),BI11&gt;=$D$75),OR(ISBLANK(BI48),BI48&gt;=$D$76)),MAX(0,BI18-$D$74*100),0)</f>
       </c>
       <c r="BJ16" s="42">
-        <f>IF(AND(12&gt;=($D$78-1),OR(ISBLANK(BJ11),BJ11&gt;=$D$76),OR(ISBLANK(BJ48),BJ48&gt;=$D$77)),MAX(0,BJ18-$D$75*100),0)</f>
+        <f>IF(AND(12&gt;=($D$77-1),OR(ISBLANK(BJ11),BJ11&gt;=$D$75),OR(ISBLANK(BJ48),BJ48&gt;=$D$76)),MAX(0,BJ18-$D$74*100),0)</f>
       </c>
       <c r="BK16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BK11),BK11&gt;=$D$76),OR(ISBLANK(BK48),BK48&gt;=$D$77)),MAX(0,BK18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BK11),BK11&gt;=$D$75),OR(ISBLANK(BK48),BK48&gt;=$D$76)),MAX(0,BK18-$D$74*100),0)</f>
       </c>
       <c r="BL16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BL11),BL11&gt;=$D$76),OR(ISBLANK(BL48),BL48&gt;=$D$77)),MAX(0,BL18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BL11),BL11&gt;=$D$75),OR(ISBLANK(BL48),BL48&gt;=$D$76)),MAX(0,BL18-$D$74*100),0)</f>
       </c>
       <c r="BM16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BM11),BM11&gt;=$D$76),OR(ISBLANK(BM48),BM48&gt;=$D$77)),MAX(0,BM18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BM11),BM11&gt;=$D$75),OR(ISBLANK(BM48),BM48&gt;=$D$76)),MAX(0,BM18-$D$74*100),0)</f>
       </c>
       <c r="BN16" s="42">
-        <f>IF(AND(13&gt;=($D$78-1),OR(ISBLANK(BN11),BN11&gt;=$D$76),OR(ISBLANK(BN48),BN48&gt;=$D$77)),MAX(0,BN18-$D$75*100),0)</f>
+        <f>IF(AND(13&gt;=($D$77-1),OR(ISBLANK(BN11),BN11&gt;=$D$75),OR(ISBLANK(BN48),BN48&gt;=$D$76)),MAX(0,BN18-$D$74*100),0)</f>
       </c>
       <c r="BO16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BO11),BO11&gt;=$D$76),OR(ISBLANK(BO48),BO48&gt;=$D$77)),MAX(0,BO18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BO11),BO11&gt;=$D$75),OR(ISBLANK(BO48),BO48&gt;=$D$76)),MAX(0,BO18-$D$74*100),0)</f>
       </c>
       <c r="BP16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BP11),BP11&gt;=$D$76),OR(ISBLANK(BP48),BP48&gt;=$D$77)),MAX(0,BP18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BP11),BP11&gt;=$D$75),OR(ISBLANK(BP48),BP48&gt;=$D$76)),MAX(0,BP18-$D$74*100),0)</f>
       </c>
       <c r="BQ16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BQ11),BQ11&gt;=$D$76),OR(ISBLANK(BQ48),BQ48&gt;=$D$77)),MAX(0,BQ18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BQ11),BQ11&gt;=$D$75),OR(ISBLANK(BQ48),BQ48&gt;=$D$76)),MAX(0,BQ18-$D$74*100),0)</f>
       </c>
       <c r="BR16" s="42">
-        <f>IF(AND(14&gt;=($D$78-1),OR(ISBLANK(BR11),BR11&gt;=$D$76),OR(ISBLANK(BR48),BR48&gt;=$D$77)),MAX(0,BR18-$D$75*100),0)</f>
+        <f>IF(AND(14&gt;=($D$77-1),OR(ISBLANK(BR11),BR11&gt;=$D$75),OR(ISBLANK(BR48),BR48&gt;=$D$76)),MAX(0,BR18-$D$74*100),0)</f>
       </c>
       <c r="BS16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BS11),BS11&gt;=$D$76),OR(ISBLANK(BS48),BS48&gt;=$D$77)),MAX(0,BS18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BS11),BS11&gt;=$D$75),OR(ISBLANK(BS48),BS48&gt;=$D$76)),MAX(0,BS18-$D$74*100),0)</f>
       </c>
       <c r="BT16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BT11),BT11&gt;=$D$76),OR(ISBLANK(BT48),BT48&gt;=$D$77)),MAX(0,BT18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BT11),BT11&gt;=$D$75),OR(ISBLANK(BT48),BT48&gt;=$D$76)),MAX(0,BT18-$D$74*100),0)</f>
       </c>
       <c r="BU16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BU11),BU11&gt;=$D$76),OR(ISBLANK(BU48),BU48&gt;=$D$77)),MAX(0,BU18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BU11),BU11&gt;=$D$75),OR(ISBLANK(BU48),BU48&gt;=$D$76)),MAX(0,BU18-$D$74*100),0)</f>
       </c>
       <c r="BV16" s="42">
-        <f>IF(AND(15&gt;=($D$78-1),OR(ISBLANK(BV11),BV11&gt;=$D$76),OR(ISBLANK(BV48),BV48&gt;=$D$77)),MAX(0,BV18-$D$75*100),0)</f>
+        <f>IF(AND(15&gt;=($D$77-1),OR(ISBLANK(BV11),BV11&gt;=$D$75),OR(ISBLANK(BV48),BV48&gt;=$D$76)),MAX(0,BV18-$D$74*100),0)</f>
       </c>
       <c r="BW16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BW11),BW11&gt;=$D$76),OR(ISBLANK(BW48),BW48&gt;=$D$77)),MAX(0,BW18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BW11),BW11&gt;=$D$75),OR(ISBLANK(BW48),BW48&gt;=$D$76)),MAX(0,BW18-$D$74*100),0)</f>
       </c>
       <c r="BX16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BX11),BX11&gt;=$D$76),OR(ISBLANK(BX48),BX48&gt;=$D$77)),MAX(0,BX18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BX11),BX11&gt;=$D$75),OR(ISBLANK(BX48),BX48&gt;=$D$76)),MAX(0,BX18-$D$74*100),0)</f>
       </c>
       <c r="BY16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BY11),BY11&gt;=$D$76),OR(ISBLANK(BY48),BY48&gt;=$D$77)),MAX(0,BY18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BY11),BY11&gt;=$D$75),OR(ISBLANK(BY48),BY48&gt;=$D$76)),MAX(0,BY18-$D$74*100),0)</f>
       </c>
       <c r="BZ16" s="42">
-        <f>IF(AND(16&gt;=($D$78-1),OR(ISBLANK(BZ11),BZ11&gt;=$D$76),OR(ISBLANK(BZ48),BZ48&gt;=$D$77)),MAX(0,BZ18-$D$75*100),0)</f>
+        <f>IF(AND(16&gt;=($D$77-1),OR(ISBLANK(BZ11),BZ11&gt;=$D$75),OR(ISBLANK(BZ48),BZ48&gt;=$D$76)),MAX(0,BZ18-$D$74*100),0)</f>
       </c>
       <c r="CA16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CA11),CA11&gt;=$D$76),OR(ISBLANK(CA48),CA48&gt;=$D$77)),MAX(0,CA18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CA11),CA11&gt;=$D$75),OR(ISBLANK(CA48),CA48&gt;=$D$76)),MAX(0,CA18-$D$74*100),0)</f>
       </c>
       <c r="CB16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CB11),CB11&gt;=$D$76),OR(ISBLANK(CB48),CB48&gt;=$D$77)),MAX(0,CB18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CB11),CB11&gt;=$D$75),OR(ISBLANK(CB48),CB48&gt;=$D$76)),MAX(0,CB18-$D$74*100),0)</f>
       </c>
       <c r="CC16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CC11),CC11&gt;=$D$76),OR(ISBLANK(CC48),CC48&gt;=$D$77)),MAX(0,CC18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CC11),CC11&gt;=$D$75),OR(ISBLANK(CC48),CC48&gt;=$D$76)),MAX(0,CC18-$D$74*100),0)</f>
       </c>
       <c r="CD16" s="42">
-        <f>IF(AND(17&gt;=($D$78-1),OR(ISBLANK(CD11),CD11&gt;=$D$76),OR(ISBLANK(CD48),CD48&gt;=$D$77)),MAX(0,CD18-$D$75*100),0)</f>
+        <f>IF(AND(17&gt;=($D$77-1),OR(ISBLANK(CD11),CD11&gt;=$D$75),OR(ISBLANK(CD48),CD48&gt;=$D$76)),MAX(0,CD18-$D$74*100),0)</f>
       </c>
       <c r="CE16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CE11),CE11&gt;=$D$76),OR(ISBLANK(CE48),CE48&gt;=$D$77)),MAX(0,CE18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CE11),CE11&gt;=$D$75),OR(ISBLANK(CE48),CE48&gt;=$D$76)),MAX(0,CE18-$D$74*100),0)</f>
       </c>
       <c r="CF16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CF11),CF11&gt;=$D$76),OR(ISBLANK(CF48),CF48&gt;=$D$77)),MAX(0,CF18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CF11),CF11&gt;=$D$75),OR(ISBLANK(CF48),CF48&gt;=$D$76)),MAX(0,CF18-$D$74*100),0)</f>
       </c>
       <c r="CG16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CG11),CG11&gt;=$D$76),OR(ISBLANK(CG48),CG48&gt;=$D$77)),MAX(0,CG18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CG11),CG11&gt;=$D$75),OR(ISBLANK(CG48),CG48&gt;=$D$76)),MAX(0,CG18-$D$74*100),0)</f>
       </c>
       <c r="CH16" s="42">
-        <f>IF(AND(18&gt;=($D$78-1),OR(ISBLANK(CH11),CH11&gt;=$D$76),OR(ISBLANK(CH48),CH48&gt;=$D$77)),MAX(0,CH18-$D$75*100),0)</f>
+        <f>IF(AND(18&gt;=($D$77-1),OR(ISBLANK(CH11),CH11&gt;=$D$75),OR(ISBLANK(CH48),CH48&gt;=$D$76)),MAX(0,CH18-$D$74*100),0)</f>
       </c>
       <c r="CI16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CI11),CI11&gt;=$D$76),OR(ISBLANK(CI48),CI48&gt;=$D$77)),MAX(0,CI18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CI11),CI11&gt;=$D$75),OR(ISBLANK(CI48),CI48&gt;=$D$76)),MAX(0,CI18-$D$74*100),0)</f>
       </c>
       <c r="CJ16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CJ11),CJ11&gt;=$D$76),OR(ISBLANK(CJ48),CJ48&gt;=$D$77)),MAX(0,CJ18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CJ11),CJ11&gt;=$D$75),OR(ISBLANK(CJ48),CJ48&gt;=$D$76)),MAX(0,CJ18-$D$74*100),0)</f>
       </c>
       <c r="CK16" s="42">
-        <f>IF(AND(19&gt;=($D$78-1),OR(ISBLANK(CK11),CK11&gt;=$D$76),OR(ISBLANK(CK48),CK48&gt;=$D$77)),MAX(0,CK18-$D$75*100),0)</f>
+        <f>IF(AND(19&gt;=($D$77-1),OR(ISBLANK(CK11),CK11&gt;=$D$75),OR(ISBLANK(CK48),CK48&gt;=$D$76)),MAX(0,CK18-$D$74*100),0)</f>
       </c>
       <c r="CL16" s="42">
         <f>MAX(0,CL18)</f>
@@ -38495,262 +38254,262 @@
         <v>237</v>
       </c>
       <c r="E56" s="31">
-        <f>'Revenue'!E17-'Opex'!E24+'IS(Q)'!E44+'IS(Q)'!E31+'Revenue'!E22-(E79*$D$73*100)</f>
+        <f>'Revenue'!E17-'Opex'!E24+'IS(Q)'!E44+'IS(Q)'!E31+'Revenue'!E22-('Debt'!E8)</f>
       </c>
       <c r="F56" s="31">
-        <f>'Revenue'!F17-'Opex'!F24+'IS(Q)'!F44+'IS(Q)'!F31+'Revenue'!F22-(F79*$D$73*100)</f>
+        <f>'Revenue'!F17-'Opex'!F24+'IS(Q)'!F44+'IS(Q)'!F31+'Revenue'!F22-('Debt'!F8)</f>
       </c>
       <c r="G56" s="31">
-        <f>'Revenue'!G17-'Opex'!G24+'IS(Q)'!G44+'IS(Q)'!G31+'Revenue'!G22-(G79*$D$73*100)</f>
+        <f>'Revenue'!G17-'Opex'!G24+'IS(Q)'!G44+'IS(Q)'!G31+'Revenue'!G22-('Debt'!G8)</f>
       </c>
       <c r="H56" s="31">
-        <f>'Revenue'!H17-'Opex'!H24+'IS(Q)'!H44+'IS(Q)'!H31+'Revenue'!H22-(H79*$D$73*100)</f>
+        <f>'Revenue'!H17-'Opex'!H24+'IS(Q)'!H44+'IS(Q)'!H31+'Revenue'!H22-('Debt'!H8)</f>
       </c>
       <c r="I56" s="31">
-        <f>'Revenue'!I17-'Opex'!I24+'IS(Q)'!I44+'IS(Q)'!I31+'Revenue'!I22-(I79*$D$73*100)</f>
+        <f>'Revenue'!I17-'Opex'!I24+'IS(Q)'!I44+'IS(Q)'!I31+'Revenue'!I22-('Debt'!I8)</f>
       </c>
       <c r="J56" s="31">
-        <f>'Revenue'!J17-'Opex'!J24+'IS(Q)'!J44+'IS(Q)'!J31+'Revenue'!J22-(J79*$D$73*100)</f>
+        <f>'Revenue'!J17-'Opex'!J24+'IS(Q)'!J44+'IS(Q)'!J31+'Revenue'!J22-('Debt'!J8)</f>
       </c>
       <c r="K56" s="31">
-        <f>'Revenue'!K17-'Opex'!K24+'IS(Q)'!K44+'IS(Q)'!K31+'Revenue'!K22-(K79*$D$73*100)</f>
+        <f>'Revenue'!K17-'Opex'!K24+'IS(Q)'!K44+'IS(Q)'!K31+'Revenue'!K22-('Debt'!K8)</f>
       </c>
       <c r="L56" s="31">
-        <f>'Revenue'!L17-'Opex'!L24+'IS(Q)'!L44+'IS(Q)'!L31+'Revenue'!L22-(L79*$D$73*100)</f>
+        <f>'Revenue'!L17-'Opex'!L24+'IS(Q)'!L44+'IS(Q)'!L31+'Revenue'!L22-('Debt'!L8)</f>
       </c>
       <c r="M56" s="31">
-        <f>'Revenue'!M17-'Opex'!M24+'IS(Q)'!M44+'IS(Q)'!M31+'Revenue'!M22-(M79*$D$73*100)</f>
+        <f>'Revenue'!M17-'Opex'!M24+'IS(Q)'!M44+'IS(Q)'!M31+'Revenue'!M22-('Debt'!M8)</f>
       </c>
       <c r="N56" s="31">
-        <f>'Revenue'!N17-'Opex'!N24+'IS(Q)'!N44+'IS(Q)'!N31+'Revenue'!N22-(N79*$D$73*100)</f>
+        <f>'Revenue'!N17-'Opex'!N24+'IS(Q)'!N44+'IS(Q)'!N31+'Revenue'!N22-('Debt'!N8)</f>
       </c>
       <c r="O56" s="31">
-        <f>'Revenue'!O17-'Opex'!O24+'IS(Q)'!O44+'IS(Q)'!O31+'Revenue'!O22-(O79*$D$73*100)</f>
+        <f>'Revenue'!O17-'Opex'!O24+'IS(Q)'!O44+'IS(Q)'!O31+'Revenue'!O22-('Debt'!O8)</f>
       </c>
       <c r="P56" s="31">
-        <f>'Revenue'!P17-'Opex'!P24+'IS(Q)'!P44+'IS(Q)'!P31+'Revenue'!P22-(P79*$D$73*100)</f>
+        <f>'Revenue'!P17-'Opex'!P24+'IS(Q)'!P44+'IS(Q)'!P31+'Revenue'!P22-('Debt'!P8)</f>
       </c>
       <c r="Q56" s="31">
-        <f>'Revenue'!Q17-'Opex'!Q24+'IS(Q)'!Q44+'IS(Q)'!Q31+'Revenue'!Q22-(Q79*$D$73*100)</f>
+        <f>'Revenue'!Q17-'Opex'!Q24+'IS(Q)'!Q44+'IS(Q)'!Q31+'Revenue'!Q22-('Debt'!Q8)</f>
       </c>
       <c r="R56" s="31">
-        <f>'Revenue'!R17-'Opex'!R24+'IS(Q)'!R44+'IS(Q)'!R31+'Revenue'!R22-(R79*$D$73*100)</f>
+        <f>'Revenue'!R17-'Opex'!R24+'IS(Q)'!R44+'IS(Q)'!R31+'Revenue'!R22-('Debt'!R8)</f>
       </c>
       <c r="S56" s="31">
-        <f>'Revenue'!S17-'Opex'!S24+'IS(Q)'!S44+'IS(Q)'!S31+'Revenue'!S22-(S79*$D$73*100)</f>
+        <f>'Revenue'!S17-'Opex'!S24+'IS(Q)'!S44+'IS(Q)'!S31+'Revenue'!S22-('Debt'!S8)</f>
       </c>
       <c r="T56" s="31">
-        <f>'Revenue'!T17-'Opex'!T24+'IS(Q)'!T44+'IS(Q)'!T31+'Revenue'!T22-(T79*$D$73*100)</f>
+        <f>'Revenue'!T17-'Opex'!T24+'IS(Q)'!T44+'IS(Q)'!T31+'Revenue'!T22-('Debt'!T8)</f>
       </c>
       <c r="U56" s="31">
-        <f>'Revenue'!U17-'Opex'!U24+'IS(Q)'!U44+'IS(Q)'!U31+'Revenue'!U22-(U79*$D$73*100)</f>
+        <f>'Revenue'!U17-'Opex'!U24+'IS(Q)'!U44+'IS(Q)'!U31+'Revenue'!U22-('Debt'!U8)</f>
       </c>
       <c r="V56" s="31">
-        <f>'Revenue'!V17-'Opex'!V24+'IS(Q)'!V44+'IS(Q)'!V31+'Revenue'!V22-(V79*$D$73*100)</f>
+        <f>'Revenue'!V17-'Opex'!V24+'IS(Q)'!V44+'IS(Q)'!V31+'Revenue'!V22-('Debt'!V8)</f>
       </c>
       <c r="W56" s="31">
-        <f>'Revenue'!W17-'Opex'!W24+'IS(Q)'!W44+'IS(Q)'!W31+'Revenue'!W22-(W79*$D$73*100)</f>
+        <f>'Revenue'!W17-'Opex'!W24+'IS(Q)'!W44+'IS(Q)'!W31+'Revenue'!W22-('Debt'!W8)</f>
       </c>
       <c r="X56" s="31">
-        <f>'Revenue'!X17-'Opex'!X24+'IS(Q)'!X44+'IS(Q)'!X31+'Revenue'!X22-(X79*$D$73*100)</f>
+        <f>'Revenue'!X17-'Opex'!X24+'IS(Q)'!X44+'IS(Q)'!X31+'Revenue'!X22-('Debt'!X8)</f>
       </c>
       <c r="Y56" s="31">
-        <f>'Revenue'!Y17-'Opex'!Y24+'IS(Q)'!Y44+'IS(Q)'!Y31+'Revenue'!Y22-(Y79*$D$73*100)</f>
+        <f>'Revenue'!Y17-'Opex'!Y24+'IS(Q)'!Y44+'IS(Q)'!Y31+'Revenue'!Y22-('Debt'!Y8)</f>
       </c>
       <c r="Z56" s="31">
-        <f>'Revenue'!Z17-'Opex'!Z24+'IS(Q)'!Z44+'IS(Q)'!Z31+'Revenue'!Z22-(Z79*$D$73*100)</f>
+        <f>'Revenue'!Z17-'Opex'!Z24+'IS(Q)'!Z44+'IS(Q)'!Z31+'Revenue'!Z22-('Debt'!Z8)</f>
       </c>
       <c r="AA56" s="31">
-        <f>'Revenue'!AA17-'Opex'!AA24+'IS(Q)'!AA44+'IS(Q)'!AA31+'Revenue'!AA22-(AA79*$D$73*100)</f>
+        <f>'Revenue'!AA17-'Opex'!AA24+'IS(Q)'!AA44+'IS(Q)'!AA31+'Revenue'!AA22-('Debt'!AA8)</f>
       </c>
       <c r="AB56" s="31">
-        <f>'Revenue'!AB17-'Opex'!AB24+'IS(Q)'!AB44+'IS(Q)'!AB31+'Revenue'!AB22-(AB79*$D$73*100)</f>
+        <f>'Revenue'!AB17-'Opex'!AB24+'IS(Q)'!AB44+'IS(Q)'!AB31+'Revenue'!AB22-('Debt'!AB8)</f>
       </c>
       <c r="AC56" s="31">
-        <f>'Revenue'!AC17-'Opex'!AC24+'IS(Q)'!AC44+'IS(Q)'!AC31+'Revenue'!AC22-(AC79*$D$73*100)</f>
+        <f>'Revenue'!AC17-'Opex'!AC24+'IS(Q)'!AC44+'IS(Q)'!AC31+'Revenue'!AC22-('Debt'!AC8)</f>
       </c>
       <c r="AD56" s="31">
-        <f>'Revenue'!AD17-'Opex'!AD24+'IS(Q)'!AD44+'IS(Q)'!AD31+'Revenue'!AD22-(AD79*$D$73*100)</f>
+        <f>'Revenue'!AD17-'Opex'!AD24+'IS(Q)'!AD44+'IS(Q)'!AD31+'Revenue'!AD22-('Debt'!AD8)</f>
       </c>
       <c r="AE56" s="31">
-        <f>'Revenue'!AE17-'Opex'!AE24+'IS(Q)'!AE44+'IS(Q)'!AE31+'Revenue'!AE22-(AE79*$D$73*100)</f>
+        <f>'Revenue'!AE17-'Opex'!AE24+'IS(Q)'!AE44+'IS(Q)'!AE31+'Revenue'!AE22-('Debt'!AE8)</f>
       </c>
       <c r="AF56" s="31">
-        <f>'Revenue'!AF17-'Opex'!AF24+'IS(Q)'!AF44+'IS(Q)'!AF31+'Revenue'!AF22-(AF79*$D$73*100)</f>
+        <f>'Revenue'!AF17-'Opex'!AF24+'IS(Q)'!AF44+'IS(Q)'!AF31+'Revenue'!AF22-('Debt'!AF8)</f>
       </c>
       <c r="AG56" s="31">
-        <f>'Revenue'!AG17-'Opex'!AG24+'IS(Q)'!AG44+'IS(Q)'!AG31+'Revenue'!AG22-(AG79*$D$73*100)</f>
+        <f>'Revenue'!AG17-'Opex'!AG24+'IS(Q)'!AG44+'IS(Q)'!AG31+'Revenue'!AG22-('Debt'!AG8)</f>
       </c>
       <c r="AH56" s="31">
-        <f>'Revenue'!AH17-'Opex'!AH24+'IS(Q)'!AH44+'IS(Q)'!AH31+'Revenue'!AH22-(AH79*$D$73*100)</f>
+        <f>'Revenue'!AH17-'Opex'!AH24+'IS(Q)'!AH44+'IS(Q)'!AH31+'Revenue'!AH22-('Debt'!AH8)</f>
       </c>
       <c r="AI56" s="31">
-        <f>'Revenue'!AI17-'Opex'!AI24+'IS(Q)'!AI44+'IS(Q)'!AI31+'Revenue'!AI22-(AI79*$D$73*100)</f>
+        <f>'Revenue'!AI17-'Opex'!AI24+'IS(Q)'!AI44+'IS(Q)'!AI31+'Revenue'!AI22-('Debt'!AI8)</f>
       </c>
       <c r="AJ56" s="31">
-        <f>'Revenue'!AJ17-'Opex'!AJ24+'IS(Q)'!AJ44+'IS(Q)'!AJ31+'Revenue'!AJ22-(AJ79*$D$73*100)</f>
+        <f>'Revenue'!AJ17-'Opex'!AJ24+'IS(Q)'!AJ44+'IS(Q)'!AJ31+'Revenue'!AJ22-('Debt'!AJ8)</f>
       </c>
       <c r="AK56" s="31">
-        <f>'Revenue'!AK17-'Opex'!AK24+'IS(Q)'!AK44+'IS(Q)'!AK31+'Revenue'!AK22-(AK79*$D$73*100)</f>
+        <f>'Revenue'!AK17-'Opex'!AK24+'IS(Q)'!AK44+'IS(Q)'!AK31+'Revenue'!AK22-('Debt'!AK8)</f>
       </c>
       <c r="AL56" s="31">
-        <f>'Revenue'!AL17-'Opex'!AL24+'IS(Q)'!AL44+'IS(Q)'!AL31+'Revenue'!AL22-(AL79*$D$73*100)</f>
+        <f>'Revenue'!AL17-'Opex'!AL24+'IS(Q)'!AL44+'IS(Q)'!AL31+'Revenue'!AL22-('Debt'!AL8)</f>
       </c>
       <c r="AM56" s="31">
-        <f>'Revenue'!AM17-'Opex'!AM24+'IS(Q)'!AM44+'IS(Q)'!AM31+'Revenue'!AM22-(AM79*$D$73*100)</f>
+        <f>'Revenue'!AM17-'Opex'!AM24+'IS(Q)'!AM44+'IS(Q)'!AM31+'Revenue'!AM22-('Debt'!AM8)</f>
       </c>
       <c r="AN56" s="31">
-        <f>'Revenue'!AN17-'Opex'!AN24+'IS(Q)'!AN44+'IS(Q)'!AN31+'Revenue'!AN22-(AN79*$D$73*100)</f>
+        <f>'Revenue'!AN17-'Opex'!AN24+'IS(Q)'!AN44+'IS(Q)'!AN31+'Revenue'!AN22-('Debt'!AN8)</f>
       </c>
       <c r="AO56" s="31">
-        <f>'Revenue'!AO17-'Opex'!AO24+'IS(Q)'!AO44+'IS(Q)'!AO31+'Revenue'!AO22-(AO79*$D$73*100)</f>
+        <f>'Revenue'!AO17-'Opex'!AO24+'IS(Q)'!AO44+'IS(Q)'!AO31+'Revenue'!AO22-('Debt'!AO8)</f>
       </c>
       <c r="AP56" s="31">
-        <f>'Revenue'!AP17-'Opex'!AP24+'IS(Q)'!AP44+'IS(Q)'!AP31+'Revenue'!AP22-(AP79*$D$73*100)</f>
+        <f>'Revenue'!AP17-'Opex'!AP24+'IS(Q)'!AP44+'IS(Q)'!AP31+'Revenue'!AP22-('Debt'!AP8)</f>
       </c>
       <c r="AQ56" s="31">
-        <f>'Revenue'!AQ17-'Opex'!AQ24+'IS(Q)'!AQ44+'IS(Q)'!AQ31+'Revenue'!AQ22-(AQ79*$D$73*100)</f>
+        <f>'Revenue'!AQ17-'Opex'!AQ24+'IS(Q)'!AQ44+'IS(Q)'!AQ31+'Revenue'!AQ22-('Debt'!AQ8)</f>
       </c>
       <c r="AR56" s="31">
-        <f>'Revenue'!AR17-'Opex'!AR24+'IS(Q)'!AR44+'IS(Q)'!AR31+'Revenue'!AR22-(AR79*$D$73*100)</f>
+        <f>'Revenue'!AR17-'Opex'!AR24+'IS(Q)'!AR44+'IS(Q)'!AR31+'Revenue'!AR22-('Debt'!AR8)</f>
       </c>
       <c r="AS56" s="31">
-        <f>'Revenue'!AS17-'Opex'!AS24+'IS(Q)'!AS44+'IS(Q)'!AS31+'Revenue'!AS22-(AS79*$D$73*100)</f>
+        <f>'Revenue'!AS17-'Opex'!AS24+'IS(Q)'!AS44+'IS(Q)'!AS31+'Revenue'!AS22-('Debt'!AS8)</f>
       </c>
       <c r="AT56" s="31">
-        <f>'Revenue'!AT17-'Opex'!AT24+'IS(Q)'!AT44+'IS(Q)'!AT31+'Revenue'!AT22-(AT79*$D$73*100)</f>
+        <f>'Revenue'!AT17-'Opex'!AT24+'IS(Q)'!AT44+'IS(Q)'!AT31+'Revenue'!AT22-('Debt'!AT8)</f>
       </c>
       <c r="AU56" s="31">
-        <f>'Revenue'!AU17-'Opex'!AU24+'IS(Q)'!AU44+'IS(Q)'!AU31+'Revenue'!AU22-(AU79*$D$73*100)</f>
+        <f>'Revenue'!AU17-'Opex'!AU24+'IS(Q)'!AU44+'IS(Q)'!AU31+'Revenue'!AU22-('Debt'!AU8)</f>
       </c>
       <c r="AV56" s="31">
-        <f>'Revenue'!AV17-'Opex'!AV24+'IS(Q)'!AV44+'IS(Q)'!AV31+'Revenue'!AV22-(AV79*$D$73*100)</f>
+        <f>'Revenue'!AV17-'Opex'!AV24+'IS(Q)'!AV44+'IS(Q)'!AV31+'Revenue'!AV22-('Debt'!AV8)</f>
       </c>
       <c r="AW56" s="31">
-        <f>'Revenue'!AW17-'Opex'!AW24+'IS(Q)'!AW44+'IS(Q)'!AW31+'Revenue'!AW22-(AW79*$D$73*100)</f>
+        <f>'Revenue'!AW17-'Opex'!AW24+'IS(Q)'!AW44+'IS(Q)'!AW31+'Revenue'!AW22-('Debt'!AW8)</f>
       </c>
       <c r="AX56" s="31">
-        <f>'Revenue'!AX17-'Opex'!AX24+'IS(Q)'!AX44+'IS(Q)'!AX31+'Revenue'!AX22-(AX79*$D$73*100)</f>
+        <f>'Revenue'!AX17-'Opex'!AX24+'IS(Q)'!AX44+'IS(Q)'!AX31+'Revenue'!AX22-('Debt'!AX8)</f>
       </c>
       <c r="AY56" s="31">
-        <f>'Revenue'!AY17-'Opex'!AY24+'IS(Q)'!AY44+'IS(Q)'!AY31+'Revenue'!AY22-(AY79*$D$73*100)</f>
+        <f>'Revenue'!AY17-'Opex'!AY24+'IS(Q)'!AY44+'IS(Q)'!AY31+'Revenue'!AY22-('Debt'!AY8)</f>
       </c>
       <c r="AZ56" s="31">
-        <f>'Revenue'!AZ17-'Opex'!AZ24+'IS(Q)'!AZ44+'IS(Q)'!AZ31+'Revenue'!AZ22-(AZ79*$D$73*100)</f>
+        <f>'Revenue'!AZ17-'Opex'!AZ24+'IS(Q)'!AZ44+'IS(Q)'!AZ31+'Revenue'!AZ22-('Debt'!AZ8)</f>
       </c>
       <c r="BA56" s="31">
-        <f>'Revenue'!BA17-'Opex'!BA24+'IS(Q)'!BA44+'IS(Q)'!BA31+'Revenue'!BA22-(BA79*$D$73*100)</f>
+        <f>'Revenue'!BA17-'Opex'!BA24+'IS(Q)'!BA44+'IS(Q)'!BA31+'Revenue'!BA22-('Debt'!BA8)</f>
       </c>
       <c r="BB56" s="31">
-        <f>'Revenue'!BB17-'Opex'!BB24+'IS(Q)'!BB44+'IS(Q)'!BB31+'Revenue'!BB22-(BB79*$D$73*100)</f>
+        <f>'Revenue'!BB17-'Opex'!BB24+'IS(Q)'!BB44+'IS(Q)'!BB31+'Revenue'!BB22-('Debt'!BB8)</f>
       </c>
       <c r="BC56" s="31">
-        <f>'Revenue'!BC17-'Opex'!BC24+'IS(Q)'!BC44+'IS(Q)'!BC31+'Revenue'!BC22-(BC79*$D$73*100)</f>
+        <f>'Revenue'!BC17-'Opex'!BC24+'IS(Q)'!BC44+'IS(Q)'!BC31+'Revenue'!BC22-('Debt'!BC8)</f>
       </c>
       <c r="BD56" s="31">
-        <f>'Revenue'!BD17-'Opex'!BD24+'IS(Q)'!BD44+'IS(Q)'!BD31+'Revenue'!BD22-(BD79*$D$73*100)</f>
+        <f>'Revenue'!BD17-'Opex'!BD24+'IS(Q)'!BD44+'IS(Q)'!BD31+'Revenue'!BD22-('Debt'!BD8)</f>
       </c>
       <c r="BE56" s="31">
-        <f>'Revenue'!BE17-'Opex'!BE24+'IS(Q)'!BE44+'IS(Q)'!BE31+'Revenue'!BE22-(BE79*$D$73*100)</f>
+        <f>'Revenue'!BE17-'Opex'!BE24+'IS(Q)'!BE44+'IS(Q)'!BE31+'Revenue'!BE22-('Debt'!BE8)</f>
       </c>
       <c r="BF56" s="31">
-        <f>'Revenue'!BF17-'Opex'!BF24+'IS(Q)'!BF44+'IS(Q)'!BF31+'Revenue'!BF22-(BF79*$D$73*100)</f>
+        <f>'Revenue'!BF17-'Opex'!BF24+'IS(Q)'!BF44+'IS(Q)'!BF31+'Revenue'!BF22-('Debt'!BF8)</f>
       </c>
       <c r="BG56" s="31">
-        <f>'Revenue'!BG17-'Opex'!BG24+'IS(Q)'!BG44+'IS(Q)'!BG31+'Revenue'!BG22-(BG79*$D$73*100)</f>
+        <f>'Revenue'!BG17-'Opex'!BG24+'IS(Q)'!BG44+'IS(Q)'!BG31+'Revenue'!BG22-('Debt'!BG8)</f>
       </c>
       <c r="BH56" s="31">
-        <f>'Revenue'!BH17-'Opex'!BH24+'IS(Q)'!BH44+'IS(Q)'!BH31+'Revenue'!BH22-(BH79*$D$73*100)</f>
+        <f>'Revenue'!BH17-'Opex'!BH24+'IS(Q)'!BH44+'IS(Q)'!BH31+'Revenue'!BH22-('Debt'!BH8)</f>
       </c>
       <c r="BI56" s="31">
-        <f>'Revenue'!BI17-'Opex'!BI24+'IS(Q)'!BI44+'IS(Q)'!BI31+'Revenue'!BI22-(BI79*$D$73*100)</f>
+        <f>'Revenue'!BI17-'Opex'!BI24+'IS(Q)'!BI44+'IS(Q)'!BI31+'Revenue'!BI22-('Debt'!BI8)</f>
       </c>
       <c r="BJ56" s="31">
-        <f>'Revenue'!BJ17-'Opex'!BJ24+'IS(Q)'!BJ44+'IS(Q)'!BJ31+'Revenue'!BJ22-(BJ79*$D$73*100)</f>
+        <f>'Revenue'!BJ17-'Opex'!BJ24+'IS(Q)'!BJ44+'IS(Q)'!BJ31+'Revenue'!BJ22-('Debt'!BJ8)</f>
       </c>
       <c r="BK56" s="31">
-        <f>'Revenue'!BK17-'Opex'!BK24+'IS(Q)'!BK44+'IS(Q)'!BK31+'Revenue'!BK22-(BK79*$D$73*100)</f>
+        <f>'Revenue'!BK17-'Opex'!BK24+'IS(Q)'!BK44+'IS(Q)'!BK31+'Revenue'!BK22-('Debt'!BK8)</f>
       </c>
       <c r="BL56" s="31">
-        <f>'Revenue'!BL17-'Opex'!BL24+'IS(Q)'!BL44+'IS(Q)'!BL31+'Revenue'!BL22-(BL79*$D$73*100)</f>
+        <f>'Revenue'!BL17-'Opex'!BL24+'IS(Q)'!BL44+'IS(Q)'!BL31+'Revenue'!BL22-('Debt'!BL8)</f>
       </c>
       <c r="BM56" s="31">
-        <f>'Revenue'!BM17-'Opex'!BM24+'IS(Q)'!BM44+'IS(Q)'!BM31+'Revenue'!BM22-(BM79*$D$73*100)</f>
+        <f>'Revenue'!BM17-'Opex'!BM24+'IS(Q)'!BM44+'IS(Q)'!BM31+'Revenue'!BM22-('Debt'!BM8)</f>
       </c>
       <c r="BN56" s="31">
-        <f>'Revenue'!BN17-'Opex'!BN24+'IS(Q)'!BN44+'IS(Q)'!BN31+'Revenue'!BN22-(BN79*$D$73*100)</f>
+        <f>'Revenue'!BN17-'Opex'!BN24+'IS(Q)'!BN44+'IS(Q)'!BN31+'Revenue'!BN22-('Debt'!BN8)</f>
       </c>
       <c r="BO56" s="31">
-        <f>'Revenue'!BO17-'Opex'!BO24+'IS(Q)'!BO44+'IS(Q)'!BO31+'Revenue'!BO22-(BO79*$D$73*100)</f>
+        <f>'Revenue'!BO17-'Opex'!BO24+'IS(Q)'!BO44+'IS(Q)'!BO31+'Revenue'!BO22-('Debt'!BO8)</f>
       </c>
       <c r="BP56" s="31">
-        <f>'Revenue'!BP17-'Opex'!BP24+'IS(Q)'!BP44+'IS(Q)'!BP31+'Revenue'!BP22-(BP79*$D$73*100)</f>
+        <f>'Revenue'!BP17-'Opex'!BP24+'IS(Q)'!BP44+'IS(Q)'!BP31+'Revenue'!BP22-('Debt'!BP8)</f>
       </c>
       <c r="BQ56" s="31">
-        <f>'Revenue'!BQ17-'Opex'!BQ24+'IS(Q)'!BQ44+'IS(Q)'!BQ31+'Revenue'!BQ22-(BQ79*$D$73*100)</f>
+        <f>'Revenue'!BQ17-'Opex'!BQ24+'IS(Q)'!BQ44+'IS(Q)'!BQ31+'Revenue'!BQ22-('Debt'!BQ8)</f>
       </c>
       <c r="BR56" s="31">
-        <f>'Revenue'!BR17-'Opex'!BR24+'IS(Q)'!BR44+'IS(Q)'!BR31+'Revenue'!BR22-(BR79*$D$73*100)</f>
+        <f>'Revenue'!BR17-'Opex'!BR24+'IS(Q)'!BR44+'IS(Q)'!BR31+'Revenue'!BR22-('Debt'!BR8)</f>
       </c>
       <c r="BS56" s="31">
-        <f>'Revenue'!BS17-'Opex'!BS24+'IS(Q)'!BS44+'IS(Q)'!BS31+'Revenue'!BS22-(BS79*$D$73*100)</f>
+        <f>'Revenue'!BS17-'Opex'!BS24+'IS(Q)'!BS44+'IS(Q)'!BS31+'Revenue'!BS22-('Debt'!BS8)</f>
       </c>
       <c r="BT56" s="31">
-        <f>'Revenue'!BT17-'Opex'!BT24+'IS(Q)'!BT44+'IS(Q)'!BT31+'Revenue'!BT22-(BT79*$D$73*100)</f>
+        <f>'Revenue'!BT17-'Opex'!BT24+'IS(Q)'!BT44+'IS(Q)'!BT31+'Revenue'!BT22-('Debt'!BT8)</f>
       </c>
       <c r="BU56" s="31">
-        <f>'Revenue'!BU17-'Opex'!BU24+'IS(Q)'!BU44+'IS(Q)'!BU31+'Revenue'!BU22-(BU79*$D$73*100)</f>
+        <f>'Revenue'!BU17-'Opex'!BU24+'IS(Q)'!BU44+'IS(Q)'!BU31+'Revenue'!BU22-('Debt'!BU8)</f>
       </c>
       <c r="BV56" s="31">
-        <f>'Revenue'!BV17-'Opex'!BV24+'IS(Q)'!BV44+'IS(Q)'!BV31+'Revenue'!BV22-(BV79*$D$73*100)</f>
+        <f>'Revenue'!BV17-'Opex'!BV24+'IS(Q)'!BV44+'IS(Q)'!BV31+'Revenue'!BV22-('Debt'!BV8)</f>
       </c>
       <c r="BW56" s="31">
-        <f>'Revenue'!BW17-'Opex'!BW24+'IS(Q)'!BW44+'IS(Q)'!BW31+'Revenue'!BW22-(BW79*$D$73*100)</f>
+        <f>'Revenue'!BW17-'Opex'!BW24+'IS(Q)'!BW44+'IS(Q)'!BW31+'Revenue'!BW22-('Debt'!BW8)</f>
       </c>
       <c r="BX56" s="31">
-        <f>'Revenue'!BX17-'Opex'!BX24+'IS(Q)'!BX44+'IS(Q)'!BX31+'Revenue'!BX22-(BX79*$D$73*100)</f>
+        <f>'Revenue'!BX17-'Opex'!BX24+'IS(Q)'!BX44+'IS(Q)'!BX31+'Revenue'!BX22-('Debt'!BX8)</f>
       </c>
       <c r="BY56" s="31">
-        <f>'Revenue'!BY17-'Opex'!BY24+'IS(Q)'!BY44+'IS(Q)'!BY31+'Revenue'!BY22-(BY79*$D$73*100)</f>
+        <f>'Revenue'!BY17-'Opex'!BY24+'IS(Q)'!BY44+'IS(Q)'!BY31+'Revenue'!BY22-('Debt'!BY8)</f>
       </c>
       <c r="BZ56" s="31">
-        <f>'Revenue'!BZ17-'Opex'!BZ24+'IS(Q)'!BZ44+'IS(Q)'!BZ31+'Revenue'!BZ22-(BZ79*$D$73*100)</f>
+        <f>'Revenue'!BZ17-'Opex'!BZ24+'IS(Q)'!BZ44+'IS(Q)'!BZ31+'Revenue'!BZ22-('Debt'!BZ8)</f>
       </c>
       <c r="CA56" s="31">
-        <f>'Revenue'!CA17-'Opex'!CA24+'IS(Q)'!CA44+'IS(Q)'!CA31+'Revenue'!CA22-(CA79*$D$73*100)</f>
+        <f>'Revenue'!CA17-'Opex'!CA24+'IS(Q)'!CA44+'IS(Q)'!CA31+'Revenue'!CA22-('Debt'!CA8)</f>
       </c>
       <c r="CB56" s="31">
-        <f>'Revenue'!CB17-'Opex'!CB24+'IS(Q)'!CB44+'IS(Q)'!CB31+'Revenue'!CB22-(CB79*$D$73*100)</f>
+        <f>'Revenue'!CB17-'Opex'!CB24+'IS(Q)'!CB44+'IS(Q)'!CB31+'Revenue'!CB22-('Debt'!CB8)</f>
       </c>
       <c r="CC56" s="31">
-        <f>'Revenue'!CC17-'Opex'!CC24+'IS(Q)'!CC44+'IS(Q)'!CC31+'Revenue'!CC22-(CC79*$D$73*100)</f>
+        <f>'Revenue'!CC17-'Opex'!CC24+'IS(Q)'!CC44+'IS(Q)'!CC31+'Revenue'!CC22-('Debt'!CC8)</f>
       </c>
       <c r="CD56" s="31">
-        <f>'Revenue'!CD17-'Opex'!CD24+'IS(Q)'!CD44+'IS(Q)'!CD31+'Revenue'!CD22-(CD79*$D$73*100)</f>
+        <f>'Revenue'!CD17-'Opex'!CD24+'IS(Q)'!CD44+'IS(Q)'!CD31+'Revenue'!CD22-('Debt'!CD8)</f>
       </c>
       <c r="CE56" s="31">
-        <f>'Revenue'!CE17-'Opex'!CE24+'IS(Q)'!CE44+'IS(Q)'!CE31+'Revenue'!CE22-(CE79*$D$73*100)</f>
+        <f>'Revenue'!CE17-'Opex'!CE24+'IS(Q)'!CE44+'IS(Q)'!CE31+'Revenue'!CE22-('Debt'!CE8)</f>
       </c>
       <c r="CF56" s="31">
-        <f>'Revenue'!CF17-'Opex'!CF24+'IS(Q)'!CF44+'IS(Q)'!CF31+'Revenue'!CF22-(CF79*$D$73*100)</f>
+        <f>'Revenue'!CF17-'Opex'!CF24+'IS(Q)'!CF44+'IS(Q)'!CF31+'Revenue'!CF22-('Debt'!CF8)</f>
       </c>
       <c r="CG56" s="31">
-        <f>'Revenue'!CG17-'Opex'!CG24+'IS(Q)'!CG44+'IS(Q)'!CG31+'Revenue'!CG22-(CG79*$D$73*100)</f>
+        <f>'Revenue'!CG17-'Opex'!CG24+'IS(Q)'!CG44+'IS(Q)'!CG31+'Revenue'!CG22-('Debt'!CG8)</f>
       </c>
       <c r="CH56" s="31">
-        <f>'Revenue'!CH17-'Opex'!CH24+'IS(Q)'!CH44+'IS(Q)'!CH31+'Revenue'!CH22-(CH79*$D$73*100)</f>
+        <f>'Revenue'!CH17-'Opex'!CH24+'IS(Q)'!CH44+'IS(Q)'!CH31+'Revenue'!CH22-('Debt'!CH8)</f>
       </c>
       <c r="CI56" s="31">
-        <f>'Revenue'!CI17-'Opex'!CI24+'IS(Q)'!CI44+'IS(Q)'!CI31+'Revenue'!CI22-(CI79*$D$73*100)</f>
+        <f>'Revenue'!CI17-'Opex'!CI24+'IS(Q)'!CI44+'IS(Q)'!CI31+'Revenue'!CI22-('Debt'!CI8)</f>
       </c>
       <c r="CJ56" s="31">
-        <f>'Revenue'!CJ17-'Opex'!CJ24+'IS(Q)'!CJ44+'IS(Q)'!CJ31+'Revenue'!CJ22-(CJ79*$D$73*100)</f>
+        <f>'Revenue'!CJ17-'Opex'!CJ24+'IS(Q)'!CJ44+'IS(Q)'!CJ31+'Revenue'!CJ22-('Debt'!CJ8)</f>
       </c>
       <c r="CK56" s="31">
-        <f>'Revenue'!CK17-'Opex'!CK24+'IS(Q)'!CK44+'IS(Q)'!CK31+'Revenue'!CK22-(CK79*$D$73*100)</f>
+        <f>'Revenue'!CK17-'Opex'!CK24+'IS(Q)'!CK44+'IS(Q)'!CK31+'Revenue'!CK22-('Debt'!CK8)</f>
       </c>
       <c r="CL56" s="31">
-        <f>'Revenue'!CL17-'Opex'!CL24+'IS(Q)'!CL44-$D$74*100+'IS(Q)'!CL31+'Revenue'!CL22-(CL79*$D$73*100)</f>
+        <f>'Revenue'!CL17-'Opex'!CL24+'IS(Q)'!CL44-$D$73*100+'IS(Q)'!CL31+'Revenue'!CL22-('Debt'!CL8)</f>
       </c>
     </row>
     <row r="57" spans="2:90" x14ac:dyDescent="0.25">
@@ -38761,262 +38520,262 @@
         <v>237</v>
       </c>
       <c r="E57" s="31">
-        <f>'Revenue'!E17-'Opex'!E24+'IS(Q)'!E31+'Revenue'!E22-(E79*$D$73*100)</f>
+        <f>'Revenue'!E17-'Opex'!E24+'IS(Q)'!E31+'Revenue'!E22-('Debt'!E8)</f>
       </c>
       <c r="F57" s="31">
-        <f>'Revenue'!F17-'Opex'!F24+'IS(Q)'!F31+'Revenue'!F22-(F79*$D$73*100)</f>
+        <f>'Revenue'!F17-'Opex'!F24+'IS(Q)'!F31+'Revenue'!F22-('Debt'!F8)</f>
       </c>
       <c r="G57" s="31">
-        <f>'Revenue'!G17-'Opex'!G24+'IS(Q)'!G31+'Revenue'!G22-(G79*$D$73*100)</f>
+        <f>'Revenue'!G17-'Opex'!G24+'IS(Q)'!G31+'Revenue'!G22-('Debt'!G8)</f>
       </c>
       <c r="H57" s="31">
-        <f>'Revenue'!H17-'Opex'!H24+'IS(Q)'!H31+'Revenue'!H22-(H79*$D$73*100)</f>
+        <f>'Revenue'!H17-'Opex'!H24+'IS(Q)'!H31+'Revenue'!H22-('Debt'!H8)</f>
       </c>
       <c r="I57" s="31">
-        <f>'Revenue'!I17-'Opex'!I24+'IS(Q)'!I31+'Revenue'!I22-(I79*$D$73*100)</f>
+        <f>'Revenue'!I17-'Opex'!I24+'IS(Q)'!I31+'Revenue'!I22-('Debt'!I8)</f>
       </c>
       <c r="J57" s="31">
-        <f>'Revenue'!J17-'Opex'!J24+'IS(Q)'!J31+'Revenue'!J22-(J79*$D$73*100)</f>
+        <f>'Revenue'!J17-'Opex'!J24+'IS(Q)'!J31+'Revenue'!J22-('Debt'!J8)</f>
       </c>
       <c r="K57" s="31">
-        <f>'Revenue'!K17-'Opex'!K24+'IS(Q)'!K31+'Revenue'!K22-(K79*$D$73*100)</f>
+        <f>'Revenue'!K17-'Opex'!K24+'IS(Q)'!K31+'Revenue'!K22-('Debt'!K8)</f>
       </c>
       <c r="L57" s="31">
-        <f>'Revenue'!L17-'Opex'!L24+'IS(Q)'!L31+'Revenue'!L22-(L79*$D$73*100)</f>
+        <f>'Revenue'!L17-'Opex'!L24+'IS(Q)'!L31+'Revenue'!L22-('Debt'!L8)</f>
       </c>
       <c r="M57" s="31">
-        <f>'Revenue'!M17-'Opex'!M24+'IS(Q)'!M31+'Revenue'!M22-(M79*$D$73*100)</f>
+        <f>'Revenue'!M17-'Opex'!M24+'IS(Q)'!M31+'Revenue'!M22-('Debt'!M8)</f>
       </c>
       <c r="N57" s="31">
-        <f>'Revenue'!N17-'Opex'!N24+'IS(Q)'!N31+'Revenue'!N22-(N79*$D$73*100)</f>
+        <f>'Revenue'!N17-'Opex'!N24+'IS(Q)'!N31+'Revenue'!N22-('Debt'!N8)</f>
       </c>
       <c r="O57" s="31">
-        <f>'Revenue'!O17-'Opex'!O24+'IS(Q)'!O31+'Revenue'!O22-(O79*$D$73*100)</f>
+        <f>'Revenue'!O17-'Opex'!O24+'IS(Q)'!O31+'Revenue'!O22-('Debt'!O8)</f>
       </c>
       <c r="P57" s="31">
-        <f>'Revenue'!P17-'Opex'!P24+'IS(Q)'!P31+'Revenue'!P22-(P79*$D$73*100)</f>
+        <f>'Revenue'!P17-'Opex'!P24+'IS(Q)'!P31+'Revenue'!P22-('Debt'!P8)</f>
       </c>
       <c r="Q57" s="31">
-        <f>'Revenue'!Q17-'Opex'!Q24+'IS(Q)'!Q31+'Revenue'!Q22-(Q79*$D$73*100)</f>
+        <f>'Revenue'!Q17-'Opex'!Q24+'IS(Q)'!Q31+'Revenue'!Q22-('Debt'!Q8)</f>
       </c>
       <c r="R57" s="31">
-        <f>'Revenue'!R17-'Opex'!R24+'IS(Q)'!R31+'Revenue'!R22-(R79*$D$73*100)</f>
+        <f>'Revenue'!R17-'Opex'!R24+'IS(Q)'!R31+'Revenue'!R22-('Debt'!R8)</f>
       </c>
       <c r="S57" s="31">
-        <f>'Revenue'!S17-'Opex'!S24+'IS(Q)'!S31+'Revenue'!S22-(S79*$D$73*100)</f>
+        <f>'Revenue'!S17-'Opex'!S24+'IS(Q)'!S31+'Revenue'!S22-('Debt'!S8)</f>
       </c>
       <c r="T57" s="31">
-        <f>'Revenue'!T17-'Opex'!T24+'IS(Q)'!T31+'Revenue'!T22-(T79*$D$73*100)</f>
+        <f>'Revenue'!T17-'Opex'!T24+'IS(Q)'!T31+'Revenue'!T22-('Debt'!T8)</f>
       </c>
       <c r="U57" s="31">
-        <f>'Revenue'!U17-'Opex'!U24+'IS(Q)'!U31+'Revenue'!U22-(U79*$D$73*100)</f>
+        <f>'Revenue'!U17-'Opex'!U24+'IS(Q)'!U31+'Revenue'!U22-('Debt'!U8)</f>
       </c>
       <c r="V57" s="31">
-        <f>'Revenue'!V17-'Opex'!V24+'IS(Q)'!V31+'Revenue'!V22-(V79*$D$73*100)</f>
+        <f>'Revenue'!V17-'Opex'!V24+'IS(Q)'!V31+'Revenue'!V22-('Debt'!V8)</f>
       </c>
       <c r="W57" s="31">
-        <f>'Revenue'!W17-'Opex'!W24+'IS(Q)'!W31+'Revenue'!W22-(W79*$D$73*100)</f>
+        <f>'Revenue'!W17-'Opex'!W24+'IS(Q)'!W31+'Revenue'!W22-('Debt'!W8)</f>
       </c>
       <c r="X57" s="31">
-        <f>'Revenue'!X17-'Opex'!X24+'IS(Q)'!X31+'Revenue'!X22-(X79*$D$73*100)</f>
+        <f>'Revenue'!X17-'Opex'!X24+'IS(Q)'!X31+'Revenue'!X22-('Debt'!X8)</f>
       </c>
       <c r="Y57" s="31">
-        <f>'Revenue'!Y17-'Opex'!Y24+'IS(Q)'!Y31+'Revenue'!Y22-(Y79*$D$73*100)</f>
+        <f>'Revenue'!Y17-'Opex'!Y24+'IS(Q)'!Y31+'Revenue'!Y22-('Debt'!Y8)</f>
       </c>
       <c r="Z57" s="31">
-        <f>'Revenue'!Z17-'Opex'!Z24+'IS(Q)'!Z31+'Revenue'!Z22-(Z79*$D$73*100)</f>
+        <f>'Revenue'!Z17-'Opex'!Z24+'IS(Q)'!Z31+'Revenue'!Z22-('Debt'!Z8)</f>
       </c>
       <c r="AA57" s="31">
-        <f>'Revenue'!AA17-'Opex'!AA24+'IS(Q)'!AA31+'Revenue'!AA22-(AA79*$D$73*100)</f>
+        <f>'Revenue'!AA17-'Opex'!AA24+'IS(Q)'!AA31+'Revenue'!AA22-('Debt'!AA8)</f>
       </c>
       <c r="AB57" s="31">
-        <f>'Revenue'!AB17-'Opex'!AB24+'IS(Q)'!AB31+'Revenue'!AB22-(AB79*$D$73*100)</f>
+        <f>'Revenue'!AB17-'Opex'!AB24+'IS(Q)'!AB31+'Revenue'!AB22-('Debt'!AB8)</f>
       </c>
       <c r="AC57" s="31">
-        <f>'Revenue'!AC17-'Opex'!AC24+'IS(Q)'!AC31+'Revenue'!AC22-(AC79*$D$73*100)</f>
+        <f>'Revenue'!AC17-'Opex'!AC24+'IS(Q)'!AC31+'Revenue'!AC22-('Debt'!AC8)</f>
       </c>
       <c r="AD57" s="31">
-        <f>'Revenue'!AD17-'Opex'!AD24+'IS(Q)'!AD31+'Revenue'!AD22-(AD79*$D$73*100)</f>
+        <f>'Revenue'!AD17-'Opex'!AD24+'IS(Q)'!AD31+'Revenue'!AD22-('Debt'!AD8)</f>
       </c>
       <c r="AE57" s="31">
-        <f>'Revenue'!AE17-'Opex'!AE24+'IS(Q)'!AE31+'Revenue'!AE22-(AE79*$D$73*100)</f>
+        <f>'Revenue'!AE17-'Opex'!AE24+'IS(Q)'!AE31+'Revenue'!AE22-('Debt'!AE8)</f>
       </c>
       <c r="AF57" s="31">
-        <f>'Revenue'!AF17-'Opex'!AF24+'IS(Q)'!AF31+'Revenue'!AF22-(AF79*$D$73*100)</f>
+        <f>'Revenue'!AF17-'Opex'!AF24+'IS(Q)'!AF31+'Revenue'!AF22-('Debt'!AF8)</f>
       </c>
       <c r="AG57" s="31">
-        <f>'Revenue'!AG17-'Opex'!AG24+'IS(Q)'!AG31+'Revenue'!AG22-(AG79*$D$73*100)</f>
+        <f>'Revenue'!AG17-'Opex'!AG24+'IS(Q)'!AG31+'Revenue'!AG22-('Debt'!AG8)</f>
       </c>
       <c r="AH57" s="31">
-        <f>'Revenue'!AH17-'Opex'!AH24+'IS(Q)'!AH31+'Revenue'!AH22-(AH79*$D$73*100)</f>
+        <f>'Revenue'!AH17-'Opex'!AH24+'IS(Q)'!AH31+'Revenue'!AH22-('Debt'!AH8)</f>
       </c>
       <c r="AI57" s="31">
-        <f>'Revenue'!AI17-'Opex'!AI24+'IS(Q)'!AI31+'Revenue'!AI22-(AI79*$D$73*100)</f>
+        <f>'Revenue'!AI17-'Opex'!AI24+'IS(Q)'!AI31+'Revenue'!AI22-('Debt'!AI8)</f>
       </c>
       <c r="AJ57" s="31">
-        <f>'Revenue'!AJ17-'Opex'!AJ24+'IS(Q)'!AJ31+'Revenue'!AJ22-(AJ79*$D$73*100)</f>
+        <f>'Revenue'!AJ17-'Opex'!AJ24+'IS(Q)'!AJ31+'Revenue'!AJ22-('Debt'!AJ8)</f>
       </c>
       <c r="AK57" s="31">
-        <f>'Revenue'!AK17-'Opex'!AK24+'IS(Q)'!AK31+'Revenue'!AK22-(AK79*$D$73*100)</f>
+        <f>'Revenue'!AK17-'Opex'!AK24+'IS(Q)'!AK31+'Revenue'!AK22-('Debt'!AK8)</f>
       </c>
       <c r="AL57" s="31">
-        <f>'Revenue'!AL17-'Opex'!AL24+'IS(Q)'!AL31+'Revenue'!AL22-(AL79*$D$73*100)</f>
+        <f>'Revenue'!AL17-'Opex'!AL24+'IS(Q)'!AL31+'Revenue'!AL22-('Debt'!AL8)</f>
       </c>
       <c r="AM57" s="31">
-        <f>'Revenue'!AM17-'Opex'!AM24+'IS(Q)'!AM31+'Revenue'!AM22-(AM79*$D$73*100)</f>
+        <f>'Revenue'!AM17-'Opex'!AM24+'IS(Q)'!AM31+'Revenue'!AM22-('Debt'!AM8)</f>
       </c>
       <c r="AN57" s="31">
-        <f>'Revenue'!AN17-'Opex'!AN24+'IS(Q)'!AN31+'Revenue'!AN22-(AN79*$D$73*100)</f>
+        <f>'Revenue'!AN17-'Opex'!AN24+'IS(Q)'!AN31+'Revenue'!AN22-('Debt'!AN8)</f>
       </c>
       <c r="AO57" s="31">
-        <f>'Revenue'!AO17-'Opex'!AO24+'IS(Q)'!AO31+'Revenue'!AO22-(AO79*$D$73*100)</f>
+        <f>'Revenue'!AO17-'Opex'!AO24+'IS(Q)'!AO31+'Revenue'!AO22-('Debt'!AO8)</f>
       </c>
       <c r="AP57" s="31">
-        <f>'Revenue'!AP17-'Opex'!AP24+'IS(Q)'!AP31+'Revenue'!AP22-(AP79*$D$73*100)</f>
+        <f>'Revenue'!AP17-'Opex'!AP24+'IS(Q)'!AP31+'Revenue'!AP22-('Debt'!AP8)</f>
       </c>
       <c r="AQ57" s="31">
-        <f>'Revenue'!AQ17-'Opex'!AQ24+'IS(Q)'!AQ31+'Revenue'!AQ22-(AQ79*$D$73*100)</f>
+        <f>'Revenue'!AQ17-'Opex'!AQ24+'IS(Q)'!AQ31+'Revenue'!AQ22-('Debt'!AQ8)</f>
       </c>
       <c r="AR57" s="31">
-        <f>'Revenue'!AR17-'Opex'!AR24+'IS(Q)'!AR31+'Revenue'!AR22-(AR79*$D$73*100)</f>
+        <f>'Revenue'!AR17-'Opex'!AR24+'IS(Q)'!AR31+'Revenue'!AR22-('Debt'!AR8)</f>
       </c>
       <c r="AS57" s="31">
-        <f>'Revenue'!AS17-'Opex'!AS24+'IS(Q)'!AS31+'Revenue'!AS22-(AS79*$D$73*100)</f>
+        <f>'Revenue'!AS17-'Opex'!AS24+'IS(Q)'!AS31+'Revenue'!AS22-('Debt'!AS8)</f>
       </c>
       <c r="AT57" s="31">
-        <f>'Revenue'!AT17-'Opex'!AT24+'IS(Q)'!AT31+'Revenue'!AT22-(AT79*$D$73*100)</f>
+        <f>'Revenue'!AT17-'Opex'!AT24+'IS(Q)'!AT31+'Revenue'!AT22-('Debt'!AT8)</f>
       </c>
       <c r="AU57" s="31">
-        <f>'Revenue'!AU17-'Opex'!AU24+'IS(Q)'!AU31+'Revenue'!AU22-(AU79*$D$73*100)</f>
+        <f>'Revenue'!AU17-'Opex'!AU24+'IS(Q)'!AU31+'Revenue'!AU22-('Debt'!AU8)</f>
       </c>
       <c r="AV57" s="31">
-        <f>'Revenue'!AV17-'Opex'!AV24+'IS(Q)'!AV31+'Revenue'!AV22-(AV79*$D$73*100)</f>
+        <f>'Revenue'!AV17-'Opex'!AV24+'IS(Q)'!AV31+'Revenue'!AV22-('Debt'!AV8)</f>
       </c>
       <c r="AW57" s="31">
-        <f>'Revenue'!AW17-'Opex'!AW24+'IS(Q)'!AW31+'Revenue'!AW22-(AW79*$D$73*100)</f>
+        <f>'Revenue'!AW17-'Opex'!AW24+'IS(Q)'!AW31+'Revenue'!AW22-('Debt'!AW8)</f>
       </c>
       <c r="AX57" s="31">
-        <f>'Revenue'!AX17-'Opex'!AX24+'IS(Q)'!AX31+'Revenue'!AX22-(AX79*$D$73*100)</f>
+        <f>'Revenue'!AX17-'Opex'!AX24+'IS(Q)'!AX31+'Revenue'!AX22-('Debt'!AX8)</f>
       </c>
       <c r="AY57" s="31">
-        <f>'Revenue'!AY17-'Opex'!AY24+'IS(Q)'!AY31+'Revenue'!AY22-(AY79*$D$73*100)</f>
+        <f>'Revenue'!AY17-'Opex'!AY24+'IS(Q)'!AY31+'Revenue'!AY22-('Debt'!AY8)</f>
       </c>
       <c r="AZ57" s="31">
-        <f>'Revenue'!AZ17-'Opex'!AZ24+'IS(Q)'!AZ31+'Revenue'!AZ22-(AZ79*$D$73*100)</f>
+        <f>'Revenue'!AZ17-'Opex'!AZ24+'IS(Q)'!AZ31+'Revenue'!AZ22-('Debt'!AZ8)</f>
       </c>
       <c r="BA57" s="31">
-        <f>'Revenue'!BA17-'Opex'!BA24+'IS(Q)'!BA31+'Revenue'!BA22-(BA79*$D$73*100)</f>
+        <f>'Revenue'!BA17-'Opex'!BA24+'IS(Q)'!BA31+'Revenue'!BA22-('Debt'!BA8)</f>
       </c>
       <c r="BB57" s="31">
-        <f>'Revenue'!BB17-'Opex'!BB24+'IS(Q)'!BB31+'Revenue'!BB22-(BB79*$D$73*100)</f>
+        <f>'Revenue'!BB17-'Opex'!BB24+'IS(Q)'!BB31+'Revenue'!BB22-('Debt'!BB8)</f>
       </c>
       <c r="BC57" s="31">
-        <f>'Revenue'!BC17-'Opex'!BC24+'IS(Q)'!BC31+'Revenue'!BC22-(BC79*$D$73*100)</f>
+        <f>'Revenue'!BC17-'Opex'!BC24+'IS(Q)'!BC31+'Revenue'!BC22-('Debt'!BC8)</f>
       </c>
       <c r="BD57" s="31">
-        <f>'Revenue'!BD17-'Opex'!BD24+'IS(Q)'!BD31+'Revenue'!BD22-(BD79*$D$73*100)</f>
+        <f>'Revenue'!BD17-'Opex'!BD24+'IS(Q)'!BD31+'Revenue'!BD22-('Debt'!BD8)</f>
       </c>
       <c r="BE57" s="31">
-        <f>'Revenue'!BE17-'Opex'!BE24+'IS(Q)'!BE31+'Revenue'!BE22-(BE79*$D$73*100)</f>
+        <f>'Revenue'!BE17-'Opex'!BE24+'IS(Q)'!BE31+'Revenue'!BE22-('Debt'!BE8)</f>
       </c>
       <c r="BF57" s="31">
-        <f>'Revenue'!BF17-'Opex'!BF24+'IS(Q)'!BF31+'Revenue'!BF22-(BF79*$D$73*100)</f>
+        <f>'Revenue'!BF17-'Opex'!BF24+'IS(Q)'!BF31+'Revenue'!BF22-('Debt'!BF8)</f>
       </c>
       <c r="BG57" s="31">
-        <f>'Revenue'!BG17-'Opex'!BG24+'IS(Q)'!BG31+'Revenue'!BG22-(BG79*$D$73*100)</f>
+        <f>'Revenue'!BG17-'Opex'!BG24+'IS(Q)'!BG31+'Revenue'!BG22-('Debt'!BG8)</f>
       </c>
       <c r="BH57" s="31">
-        <f>'Revenue'!BH17-'Opex'!BH24+'IS(Q)'!BH31+'Revenue'!BH22-(BH79*$D$73*100)</f>
+        <f>'Revenue'!BH17-'Opex'!BH24+'IS(Q)'!BH31+'Revenue'!BH22-('Debt'!BH8)</f>
       </c>
       <c r="BI57" s="31">
-        <f>'Revenue'!BI17-'Opex'!BI24+'IS(Q)'!BI31+'Revenue'!BI22-(BI79*$D$73*100)</f>
+        <f>'Revenue'!BI17-'Opex'!BI24+'IS(Q)'!BI31+'Revenue'!BI22-('Debt'!BI8)</f>
       </c>
       <c r="BJ57" s="31">
-        <f>'Revenue'!BJ17-'Opex'!BJ24+'IS(Q)'!BJ31+'Revenue'!BJ22-(BJ79*$D$73*100)</f>
+        <f>'Revenue'!BJ17-'Opex'!BJ24+'IS(Q)'!BJ31+'Revenue'!BJ22-('Debt'!BJ8)</f>
       </c>
       <c r="BK57" s="31">
-        <f>'Revenue'!BK17-'Opex'!BK24+'IS(Q)'!BK31+'Revenue'!BK22-(BK79*$D$73*100)</f>
+        <f>'Revenue'!BK17-'Opex'!BK24+'IS(Q)'!BK31+'Revenue'!BK22-('Debt'!BK8)</f>
       </c>
       <c r="BL57" s="31">
-        <f>'Revenue'!BL17-'Opex'!BL24+'IS(Q)'!BL31+'Revenue'!BL22-(BL79*$D$73*100)</f>
+        <f>'Revenue'!BL17-'Opex'!BL24+'IS(Q)'!BL31+'Revenue'!BL22-('Debt'!BL8)</f>
       </c>
       <c r="BM57" s="31">
-        <f>'Revenue'!BM17-'Opex'!BM24+'IS(Q)'!BM31+'Revenue'!BM22-(BM79*$D$73*100)</f>
+        <f>'Revenue'!BM17-'Opex'!BM24+'IS(Q)'!BM31+'Revenue'!BM22-('Debt'!BM8)</f>
       </c>
       <c r="BN57" s="31">
-        <f>'Revenue'!BN17-'Opex'!BN24+'IS(Q)'!BN31+'Revenue'!BN22-(BN79*$D$73*100)</f>
+        <f>'Revenue'!BN17-'Opex'!BN24+'IS(Q)'!BN31+'Revenue'!BN22-('Debt'!BN8)</f>
       </c>
       <c r="BO57" s="31">
-        <f>'Revenue'!BO17-'Opex'!BO24+'IS(Q)'!BO31+'Revenue'!BO22-(BO79*$D$73*100)</f>
+        <f>'Revenue'!BO17-'Opex'!BO24+'IS(Q)'!BO31+'Revenue'!BO22-('Debt'!BO8)</f>
       </c>
       <c r="BP57" s="31">
-        <f>'Revenue'!BP17-'Opex'!BP24+'IS(Q)'!BP31+'Revenue'!BP22-(BP79*$D$73*100)</f>
+        <f>'Revenue'!BP17-'Opex'!BP24+'IS(Q)'!BP31+'Revenue'!BP22-('Debt'!BP8)</f>
       </c>
       <c r="BQ57" s="31">
-        <f>'Revenue'!BQ17-'Opex'!BQ24+'IS(Q)'!BQ31+'Revenue'!BQ22-(BQ79*$D$73*100)</f>
+        <f>'Revenue'!BQ17-'Opex'!BQ24+'IS(Q)'!BQ31+'Revenue'!BQ22-('Debt'!BQ8)</f>
       </c>
       <c r="BR57" s="31">
-        <f>'Revenue'!BR17-'Opex'!BR24+'IS(Q)'!BR31+'Revenue'!BR22-(BR79*$D$73*100)</f>
+        <f>'Revenue'!BR17-'Opex'!BR24+'IS(Q)'!BR31+'Revenue'!BR22-('Debt'!BR8)</f>
       </c>
       <c r="BS57" s="31">
-        <f>'Revenue'!BS17-'Opex'!BS24+'IS(Q)'!BS31+'Revenue'!BS22-(BS79*$D$73*100)</f>
+        <f>'Revenue'!BS17-'Opex'!BS24+'IS(Q)'!BS31+'Revenue'!BS22-('Debt'!BS8)</f>
       </c>
       <c r="BT57" s="31">
-        <f>'Revenue'!BT17-'Opex'!BT24+'IS(Q)'!BT31+'Revenue'!BT22-(BT79*$D$73*100)</f>
+        <f>'Revenue'!BT17-'Opex'!BT24+'IS(Q)'!BT31+'Revenue'!BT22-('Debt'!BT8)</f>
       </c>
       <c r="BU57" s="31">
-        <f>'Revenue'!BU17-'Opex'!BU24+'IS(Q)'!BU31+'Revenue'!BU22-(BU79*$D$73*100)</f>
+        <f>'Revenue'!BU17-'Opex'!BU24+'IS(Q)'!BU31+'Revenue'!BU22-('Debt'!BU8)</f>
       </c>
       <c r="BV57" s="31">
-        <f>'Revenue'!BV17-'Opex'!BV24+'IS(Q)'!BV31+'Revenue'!BV22-(BV79*$D$73*100)</f>
+        <f>'Revenue'!BV17-'Opex'!BV24+'IS(Q)'!BV31+'Revenue'!BV22-('Debt'!BV8)</f>
       </c>
       <c r="BW57" s="31">
-        <f>'Revenue'!BW17-'Opex'!BW24+'IS(Q)'!BW31+'Revenue'!BW22-(BW79*$D$73*100)</f>
+        <f>'Revenue'!BW17-'Opex'!BW24+'IS(Q)'!BW31+'Revenue'!BW22-('Debt'!BW8)</f>
       </c>
       <c r="BX57" s="31">
-        <f>'Revenue'!BX17-'Opex'!BX24+'IS(Q)'!BX31+'Revenue'!BX22-(BX79*$D$73*100)</f>
+        <f>'Revenue'!BX17-'Opex'!BX24+'IS(Q)'!BX31+'Revenue'!BX22-('Debt'!BX8)</f>
       </c>
       <c r="BY57" s="31">
-        <f>'Revenue'!BY17-'Opex'!BY24+'IS(Q)'!BY31+'Revenue'!BY22-(BY79*$D$73*100)</f>
+        <f>'Revenue'!BY17-'Opex'!BY24+'IS(Q)'!BY31+'Revenue'!BY22-('Debt'!BY8)</f>
       </c>
       <c r="BZ57" s="31">
-        <f>'Revenue'!BZ17-'Opex'!BZ24+'IS(Q)'!BZ31+'Revenue'!BZ22-(BZ79*$D$73*100)</f>
+        <f>'Revenue'!BZ17-'Opex'!BZ24+'IS(Q)'!BZ31+'Revenue'!BZ22-('Debt'!BZ8)</f>
       </c>
       <c r="CA57" s="31">
-        <f>'Revenue'!CA17-'Opex'!CA24+'IS(Q)'!CA31+'Revenue'!CA22-(CA79*$D$73*100)</f>
+        <f>'Revenue'!CA17-'Opex'!CA24+'IS(Q)'!CA31+'Revenue'!CA22-('Debt'!CA8)</f>
       </c>
       <c r="CB57" s="31">
-        <f>'Revenue'!CB17-'Opex'!CB24+'IS(Q)'!CB31+'Revenue'!CB22-(CB79*$D$73*100)</f>
+        <f>'Revenue'!CB17-'Opex'!CB24+'IS(Q)'!CB31+'Revenue'!CB22-('Debt'!CB8)</f>
       </c>
       <c r="CC57" s="31">
-        <f>'Revenue'!CC17-'Opex'!CC24+'IS(Q)'!CC31+'Revenue'!CC22-(CC79*$D$73*100)</f>
+        <f>'Revenue'!CC17-'Opex'!CC24+'IS(Q)'!CC31+'Revenue'!CC22-('Debt'!CC8)</f>
       </c>
       <c r="CD57" s="31">
-        <f>'Revenue'!CD17-'Opex'!CD24+'IS(Q)'!CD31+'Revenue'!CD22-(CD79*$D$73*100)</f>
+        <f>'Revenue'!CD17-'Opex'!CD24+'IS(Q)'!CD31+'Revenue'!CD22-('Debt'!CD8)</f>
       </c>
       <c r="CE57" s="31">
-        <f>'Revenue'!CE17-'Opex'!CE24+'IS(Q)'!CE31+'Revenue'!CE22-(CE79*$D$73*100)</f>
+        <f>'Revenue'!CE17-'Opex'!CE24+'IS(Q)'!CE31+'Revenue'!CE22-('Debt'!CE8)</f>
       </c>
       <c r="CF57" s="31">
-        <f>'Revenue'!CF17-'Opex'!CF24+'IS(Q)'!CF31+'Revenue'!CF22-(CF79*$D$73*100)</f>
+        <f>'Revenue'!CF17-'Opex'!CF24+'IS(Q)'!CF31+'Revenue'!CF22-('Debt'!CF8)</f>
       </c>
       <c r="CG57" s="31">
-        <f>'Revenue'!CG17-'Opex'!CG24+'IS(Q)'!CG31+'Revenue'!CG22-(CG79*$D$73*100)</f>
+        <f>'Revenue'!CG17-'Opex'!CG24+'IS(Q)'!CG31+'Revenue'!CG22-('Debt'!CG8)</f>
       </c>
       <c r="CH57" s="31">
-        <f>'Revenue'!CH17-'Opex'!CH24+'IS(Q)'!CH31+'Revenue'!CH22-(CH79*$D$73*100)</f>
+        <f>'Revenue'!CH17-'Opex'!CH24+'IS(Q)'!CH31+'Revenue'!CH22-('Debt'!CH8)</f>
       </c>
       <c r="CI57" s="31">
-        <f>'Revenue'!CI17-'Opex'!CI24+'IS(Q)'!CI31+'Revenue'!CI22-(CI79*$D$73*100)</f>
+        <f>'Revenue'!CI17-'Opex'!CI24+'IS(Q)'!CI31+'Revenue'!CI22-('Debt'!CI8)</f>
       </c>
       <c r="CJ57" s="31">
-        <f>'Revenue'!CJ17-'Opex'!CJ24+'IS(Q)'!CJ31+'Revenue'!CJ22-(CJ79*$D$73*100)</f>
+        <f>'Revenue'!CJ17-'Opex'!CJ24+'IS(Q)'!CJ31+'Revenue'!CJ22-('Debt'!CJ8)</f>
       </c>
       <c r="CK57" s="31">
-        <f>'Revenue'!CK17-'Opex'!CK24+'IS(Q)'!CK31+'Revenue'!CK22-(CK79*$D$73*100)</f>
+        <f>'Revenue'!CK17-'Opex'!CK24+'IS(Q)'!CK31+'Revenue'!CK22-('Debt'!CK8)</f>
       </c>
       <c r="CL57" s="31">
-        <f>'Revenue'!CL17-'Opex'!CL24-$D$74*100+'IS(Q)'!CL31+'Revenue'!CL22-(CL79*$D$73*100)</f>
+        <f>'Revenue'!CL17-'Opex'!CL24-$D$73*100+'IS(Q)'!CL31+'Revenue'!CL22-('Debt'!CL8)</f>
       </c>
     </row>
     <row r="58" spans="2:90" x14ac:dyDescent="0.25">
@@ -39980,334 +39739,57 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="33" t="s">
-        <v>232</v>
+        <v>403</v>
       </c>
       <c r="C73" s="44" t="s">
-        <v>233</v>
+        <v>404</v>
       </c>
       <c r="D73" s="45">
-        <f>'입력값'!C8</f>
+        <f>'입력값'!C17</f>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="33" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="C74" s="44" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="D74" s="45">
-        <f>'입력값'!C17</f>
+        <f>'입력값'!C25</f>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="33" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C75" s="44" t="s">
-        <v>473</v>
-      </c>
-      <c r="D75" s="45">
-        <f>'입력값'!C25</f>
+        <v>475</v>
+      </c>
+      <c r="D75" s="66">
+        <f>'입력값'!C26</f>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="33" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C76" s="44" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D76" s="66">
-        <f>'입력값'!C26</f>
+        <f>'입력값'!C27</f>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="33" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C77" s="44" t="s">
-        <v>477</v>
-      </c>
-      <c r="D77" s="66">
-        <f>'입력값'!C27</f>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="C78" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="D78" s="67">
+      <c r="D77" s="67">
         <f>'입력값'!C28</f>
-      </c>
-    </row>
-    <row r="79" spans="2:90" x14ac:dyDescent="0.25">
-      <c r="B79" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="C79" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="E79" s="53">
-        <f>'입력값'!E57</f>
-      </c>
-      <c r="F79" s="53">
-        <f>'입력값'!F57</f>
-      </c>
-      <c r="G79" s="53">
-        <f>'입력값'!G57</f>
-      </c>
-      <c r="H79" s="53">
-        <f>'입력값'!H57</f>
-      </c>
-      <c r="I79" s="53">
-        <f>'입력값'!I57</f>
-      </c>
-      <c r="J79" s="53">
-        <f>'입력값'!J57</f>
-      </c>
-      <c r="K79" s="45">
-        <f>'입력값'!K57</f>
-      </c>
-      <c r="L79" s="45">
-        <f>'입력값'!L57</f>
-      </c>
-      <c r="M79" s="45">
-        <f>'입력값'!M57</f>
-      </c>
-      <c r="N79" s="45">
-        <f>'입력값'!N57</f>
-      </c>
-      <c r="O79" s="45">
-        <f>'입력값'!O57</f>
-      </c>
-      <c r="P79" s="45">
-        <f>'입력값'!P57</f>
-      </c>
-      <c r="Q79" s="45">
-        <f>'입력값'!Q57</f>
-      </c>
-      <c r="R79" s="45">
-        <f>'입력값'!R57</f>
-      </c>
-      <c r="S79" s="45">
-        <f>'입력값'!S57</f>
-      </c>
-      <c r="T79" s="45">
-        <f>'입력값'!T57</f>
-      </c>
-      <c r="U79" s="45">
-        <f>'입력값'!U57</f>
-      </c>
-      <c r="V79" s="45">
-        <f>'입력값'!V57</f>
-      </c>
-      <c r="W79" s="45">
-        <f>'입력값'!W57</f>
-      </c>
-      <c r="X79" s="45">
-        <f>'입력값'!X57</f>
-      </c>
-      <c r="Y79" s="45">
-        <f>'입력값'!Y57</f>
-      </c>
-      <c r="Z79" s="45">
-        <f>'입력값'!Z57</f>
-      </c>
-      <c r="AA79" s="45">
-        <f>'입력값'!AA57</f>
-      </c>
-      <c r="AB79" s="45">
-        <f>'입력값'!AB57</f>
-      </c>
-      <c r="AC79" s="45">
-        <f>'입력값'!AC57</f>
-      </c>
-      <c r="AD79" s="45">
-        <f>'입력값'!AD57</f>
-      </c>
-      <c r="AE79" s="45">
-        <f>'입력값'!AE57</f>
-      </c>
-      <c r="AF79" s="45">
-        <f>'입력값'!AF57</f>
-      </c>
-      <c r="AG79" s="45">
-        <f>'입력값'!AG57</f>
-      </c>
-      <c r="AH79" s="45">
-        <f>'입력값'!AH57</f>
-      </c>
-      <c r="AI79" s="45">
-        <f>'입력값'!AI57</f>
-      </c>
-      <c r="AJ79" s="45">
-        <f>'입력값'!AJ57</f>
-      </c>
-      <c r="AK79" s="45">
-        <f>'입력값'!AK57</f>
-      </c>
-      <c r="AL79" s="45">
-        <f>'입력값'!AL57</f>
-      </c>
-      <c r="AM79" s="45">
-        <f>'입력값'!AM57</f>
-      </c>
-      <c r="AN79" s="45">
-        <f>'입력값'!AN57</f>
-      </c>
-      <c r="AO79" s="45">
-        <f>'입력값'!AO57</f>
-      </c>
-      <c r="AP79" s="45">
-        <f>'입력값'!AP57</f>
-      </c>
-      <c r="AQ79" s="45">
-        <f>'입력값'!AQ57</f>
-      </c>
-      <c r="AR79" s="45">
-        <f>'입력값'!AR57</f>
-      </c>
-      <c r="AS79" s="45">
-        <f>'입력값'!AS57</f>
-      </c>
-      <c r="AT79" s="45">
-        <f>'입력값'!AT57</f>
-      </c>
-      <c r="AU79" s="45">
-        <f>'입력값'!AU57</f>
-      </c>
-      <c r="AV79" s="45">
-        <f>'입력값'!AV57</f>
-      </c>
-      <c r="AW79" s="45">
-        <f>'입력값'!AW57</f>
-      </c>
-      <c r="AX79" s="45">
-        <f>'입력값'!AX57</f>
-      </c>
-      <c r="AY79" s="45">
-        <f>'입력값'!AY57</f>
-      </c>
-      <c r="AZ79" s="45">
-        <f>'입력값'!AZ57</f>
-      </c>
-      <c r="BA79" s="45">
-        <f>'입력값'!BA57</f>
-      </c>
-      <c r="BB79" s="45">
-        <f>'입력값'!BB57</f>
-      </c>
-      <c r="BC79" s="45">
-        <f>'입력값'!BC57</f>
-      </c>
-      <c r="BD79" s="45">
-        <f>'입력값'!BD57</f>
-      </c>
-      <c r="BE79" s="45">
-        <f>'입력값'!BE57</f>
-      </c>
-      <c r="BF79" s="45">
-        <f>'입력값'!BF57</f>
-      </c>
-      <c r="BG79" s="45">
-        <f>'입력값'!BG57</f>
-      </c>
-      <c r="BH79" s="45">
-        <f>'입력값'!BH57</f>
-      </c>
-      <c r="BI79" s="45">
-        <f>'입력값'!BI57</f>
-      </c>
-      <c r="BJ79" s="45">
-        <f>'입력값'!BJ57</f>
-      </c>
-      <c r="BK79" s="45">
-        <f>'입력값'!BK57</f>
-      </c>
-      <c r="BL79" s="45">
-        <f>'입력값'!BL57</f>
-      </c>
-      <c r="BM79" s="45">
-        <f>'입력값'!BM57</f>
-      </c>
-      <c r="BN79" s="45">
-        <f>'입력값'!BN57</f>
-      </c>
-      <c r="BO79" s="45">
-        <f>'입력값'!BO57</f>
-      </c>
-      <c r="BP79" s="45">
-        <f>'입력값'!BP57</f>
-      </c>
-      <c r="BQ79" s="45">
-        <f>'입력값'!BQ57</f>
-      </c>
-      <c r="BR79" s="45">
-        <f>'입력값'!BR57</f>
-      </c>
-      <c r="BS79" s="45">
-        <f>'입력값'!BS57</f>
-      </c>
-      <c r="BT79" s="45">
-        <f>'입력값'!BT57</f>
-      </c>
-      <c r="BU79" s="45">
-        <f>'입력값'!BU57</f>
-      </c>
-      <c r="BV79" s="45">
-        <f>'입력값'!BV57</f>
-      </c>
-      <c r="BW79" s="45">
-        <f>'입력값'!BW57</f>
-      </c>
-      <c r="BX79" s="45">
-        <f>'입력값'!BX57</f>
-      </c>
-      <c r="BY79" s="45">
-        <f>'입력값'!BY57</f>
-      </c>
-      <c r="BZ79" s="45">
-        <f>'입력값'!BZ57</f>
-      </c>
-      <c r="CA79" s="45">
-        <f>'입력값'!CA57</f>
-      </c>
-      <c r="CB79" s="45">
-        <f>'입력값'!CB57</f>
-      </c>
-      <c r="CC79" s="45">
-        <f>'입력값'!CC57</f>
-      </c>
-      <c r="CD79" s="45">
-        <f>'입력값'!CD57</f>
-      </c>
-      <c r="CE79" s="45">
-        <f>'입력값'!CE57</f>
-      </c>
-      <c r="CF79" s="45">
-        <f>'입력값'!CF57</f>
-      </c>
-      <c r="CG79" s="45">
-        <f>'입력값'!CG57</f>
-      </c>
-      <c r="CH79" s="45">
-        <f>'입력값'!CH57</f>
-      </c>
-      <c r="CI79" s="45">
-        <f>'입력값'!CI57</f>
-      </c>
-      <c r="CJ79" s="45">
-        <f>'입력값'!CJ57</f>
-      </c>
-      <c r="CK79" s="45">
-        <f>'입력값'!CK57</f>
-      </c>
-      <c r="CL79" s="45">
-        <f>'입력값'!CL57</f>
       </c>
     </row>
   </sheetData>

--- a/dist/_sh_excel_test.xlsx
+++ b/dist/_sh_excel_test.xlsx
@@ -24,7 +24,7 @@
     <t>태양광 발전사업</t>
   </si>
   <si>
-    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-09-21</t>
+    <t>재무모델 v2 (분기·5트랜치) — 재생E AI Agent 자동생성 · 2026-09-22</t>
   </si>
   <si>
     <t>시트</t>
@@ -81,7 +81,7 @@
     <t>분기 현금흐름 · DSCR · 배당</t>
   </si>
   <si>
-    <t>※ Funding 시트의 트랜치 조건·총사업비 항목·사업자 지분은 "입력값" 시트를 참조하는 수식입니다(입력값 시트를 고치면 같이 바뀝니다). 그 외 계산 결과(세금·DSCR·배당 등)는 값(baked) 기준이라 가정을 바꾸려면 생성기에서 다시 뽑아야 합니다.</t>
+    <t>※ 입력값 시트(노란 탭) 외의 모든 값은 수식입니다. 노란 셀을 고치면 세금·DSCR·배당·IRR 까지 전부 다시 계산됩니다. 회색 셀(거치·상환·방식·투입순서, DSRA 적립기준)은 스케줄의 모양을 정하는 값이라 화면에서 다시 생성해야 합니다. 각 계산 시트 맨 아래 "가정" 블록이 입력값 시트를 참조하는 유일한 곳입니다.</t>
   </si>
   <si>
     <t>Executive Summary (v2 · 분기 · 5트랜치)</t>
@@ -693,7 +693,7 @@
     <t>총사업비 세부내역</t>
   </si>
   <si>
-    <t>합계</t>
+    <t>총사업비 (항목별 금액 미입력)</t>
   </si>
   <si>
     <t>사업자 구성 (지분)</t>
@@ -801,7 +801,7 @@
     <t>인출 시작 가정 검증</t>
   </si>
   <si>
-    <t>※ 미사용 트랜치 — 값(baked) 기준</t>
+    <t>※ 미사용 트랜치(금액 0) — 인출·상환 없음</t>
   </si>
   <si>
     <t>전체 합계</t>
